--- a/assets/data/generatordata.xlsx
+++ b/assets/data/generatordata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mthak\Desktop\pf2e-generator\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2AFD470-1795-4BEE-8ECF-632A87CFBEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACE15F5-FCB4-4AA2-84CC-29EEB3B1E559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{12225E00-D84F-438D-9971-6445E1072934}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{12225E00-D84F-438D-9971-6445E1072934}"/>
   </bookViews>
   <sheets>
     <sheet name="Ancestries" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9148" uniqueCount="2155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9156" uniqueCount="2158">
   <si>
     <t>ancestry</t>
   </si>
@@ -6513,6 +6513,15 @@
   </si>
   <si>
     <t>any</t>
+  </si>
+  <si>
+    <t>weapon_group</t>
+  </si>
+  <si>
+    <t>two-handed</t>
+  </si>
+  <si>
+    <t>specific_weapon</t>
   </si>
 </sst>
 </file>
@@ -19970,7 +19979,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60CBAAD1-70D2-405A-B142-E2A43F195251}">
-  <dimension ref="A1:L208"/>
+  <dimension ref="A1:N208"/>
   <sheetFormatPr defaultColWidth="57.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -19982,11 +19991,11 @@
     <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="16.42578125" customWidth="1"/>
-    <col min="12" max="12" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="16.42578125" customWidth="1"/>
+    <col min="14" max="14" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>807</v>
       </c>
@@ -20018,13 +20027,19 @@
         <v>394</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>2155</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>2157</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>2150</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>761</v>
       </c>
@@ -20046,11 +20061,13 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>761</v>
       </c>
@@ -20072,11 +20089,13 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>761</v>
       </c>
@@ -20098,11 +20117,13 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>761</v>
       </c>
@@ -20124,11 +20145,13 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>765</v>
       </c>
@@ -20150,11 +20173,13 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>765</v>
       </c>
@@ -20176,11 +20201,13 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>765</v>
       </c>
@@ -20202,11 +20229,13 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>765</v>
       </c>
@@ -20228,11 +20257,13 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="2" t="s">
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>770</v>
       </c>
@@ -20254,11 +20285,13 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2" t="s">
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>770</v>
       </c>
@@ -20280,11 +20313,13 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2" t="s">
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>770</v>
       </c>
@@ -20308,11 +20343,13 @@
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-      <c r="L12" s="2" t="s">
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>770</v>
       </c>
@@ -20334,11 +20371,13 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="2" t="s">
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>770</v>
       </c>
@@ -20360,11 +20399,13 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="2" t="s">
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>770</v>
       </c>
@@ -20386,11 +20427,13 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="2" t="s">
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>770</v>
       </c>
@@ -20412,11 +20455,13 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-      <c r="L16" s="2" t="s">
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>770</v>
       </c>
@@ -20440,11 +20485,13 @@
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-      <c r="L17" s="2" t="s">
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>770</v>
       </c>
@@ -20466,11 +20513,13 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="2" t="s">
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>770</v>
       </c>
@@ -20492,11 +20541,13 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-      <c r="L19" s="2" t="s">
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>773</v>
       </c>
@@ -20518,11 +20569,13 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="2" t="s">
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>773</v>
       </c>
@@ -20544,11 +20597,13 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="2" t="s">
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>773</v>
       </c>
@@ -20570,11 +20625,13 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
-      <c r="L22" s="2" t="s">
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>773</v>
       </c>
@@ -20596,11 +20653,13 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="2" t="s">
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>773</v>
       </c>
@@ -20622,11 +20681,13 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="2" t="s">
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>776</v>
       </c>
@@ -20650,11 +20711,13 @@
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="2" t="s">
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>776</v>
       </c>
@@ -20676,11 +20739,13 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-      <c r="L26" s="2" t="s">
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>776</v>
       </c>
@@ -20704,11 +20769,13 @@
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-      <c r="L27" s="2" t="s">
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>776</v>
       </c>
@@ -20730,11 +20797,13 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-      <c r="L28" s="2" t="s">
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>776</v>
       </c>
@@ -20756,11 +20825,13 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="2" t="s">
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>776</v>
       </c>
@@ -20782,11 +20853,13 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="2" t="s">
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>776</v>
       </c>
@@ -20808,11 +20881,13 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="2" t="s">
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>778</v>
       </c>
@@ -20834,11 +20909,13 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="2" t="s">
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>778</v>
       </c>
@@ -20860,11 +20937,13 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="2" t="s">
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>778</v>
       </c>
@@ -20886,11 +20965,13 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="2" t="s">
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>781</v>
       </c>
@@ -20912,11 +20993,13 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="2" t="s">
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>781</v>
       </c>
@@ -20938,11 +21021,13 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="2" t="s">
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>781</v>
       </c>
@@ -20964,11 +21049,13 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="2" t="s">
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>781</v>
       </c>
@@ -20990,11 +21077,13 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-      <c r="L38" s="2" t="s">
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>781</v>
       </c>
@@ -21016,11 +21105,13 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
-      <c r="L39" s="2" t="s">
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>781</v>
       </c>
@@ -21042,11 +21133,13 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
-      <c r="L40" s="2" t="s">
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>781</v>
       </c>
@@ -21068,11 +21161,13 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
-      <c r="L41" s="2" t="s">
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>781</v>
       </c>
@@ -21096,11 +21191,13 @@
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
-      <c r="L42" s="2" t="s">
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>781</v>
       </c>
@@ -21124,11 +21221,13 @@
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
-      <c r="L43" s="2" t="s">
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>786</v>
       </c>
@@ -21150,11 +21249,13 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
-      <c r="L44" s="2" t="s">
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>786</v>
       </c>
@@ -21176,11 +21277,13 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
-      <c r="L45" s="2" t="s">
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>786</v>
       </c>
@@ -21202,11 +21305,13 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
-      <c r="L46" s="2" t="s">
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>786</v>
       </c>
@@ -21228,11 +21333,13 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
-      <c r="L47" s="2" t="s">
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>786</v>
       </c>
@@ -21254,11 +21361,13 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
-      <c r="L48" s="2" t="s">
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>787</v>
       </c>
@@ -21280,11 +21389,13 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
-      <c r="L49" s="2" t="s">
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>787</v>
       </c>
@@ -21306,11 +21417,13 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
-      <c r="L50" s="2" t="s">
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>787</v>
       </c>
@@ -21332,11 +21445,13 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
-      <c r="L51" s="2" t="s">
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>787</v>
       </c>
@@ -21358,11 +21473,13 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
-      <c r="L52" s="2" t="s">
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>787</v>
       </c>
@@ -21384,11 +21501,13 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
-      <c r="L53" s="2" t="s">
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>787</v>
       </c>
@@ -21410,11 +21529,13 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
-      <c r="L54" s="2" t="s">
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>787</v>
       </c>
@@ -21436,11 +21557,13 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
-      <c r="L55" s="2" t="s">
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>787</v>
       </c>
@@ -21462,11 +21585,13 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
-      <c r="L56" s="2" t="s">
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>789</v>
       </c>
@@ -21487,12 +21612,16 @@
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
-      <c r="L57" s="2" t="s">
+      <c r="K57" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>789</v>
       </c>
@@ -21514,11 +21643,15 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
-      <c r="L58" s="2" t="s">
+      <c r="L58" s="2"/>
+      <c r="M58" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="N58" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>789</v>
       </c>
@@ -21540,11 +21673,13 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
-      <c r="L59" s="2" t="s">
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>789</v>
       </c>
@@ -21566,11 +21701,13 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
-      <c r="L60" s="2" t="s">
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>789</v>
       </c>
@@ -21592,11 +21729,13 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
-      <c r="L61" s="2" t="s">
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>789</v>
       </c>
@@ -21618,11 +21757,15 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
-      <c r="L62" s="2" t="s">
+      <c r="L62" s="2"/>
+      <c r="M62" s="2" t="s">
+        <v>2147</v>
+      </c>
+      <c r="N62" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>789</v>
       </c>
@@ -21645,10 +21788,14 @@
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
       <c r="L63" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>789</v>
       </c>
@@ -21670,11 +21817,13 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
-      <c r="L64" s="2" t="s">
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>793</v>
       </c>
@@ -21696,11 +21845,13 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="2" t="s">
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>793</v>
       </c>
@@ -21722,11 +21873,13 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="2" t="s">
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>793</v>
       </c>
@@ -21748,11 +21901,13 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="2" t="s">
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>793</v>
       </c>
@@ -21774,11 +21929,13 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="2" t="s">
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>793</v>
       </c>
@@ -21800,11 +21957,13 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="2" t="s">
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>793</v>
       </c>
@@ -21826,11 +21985,13 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="2" t="s">
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>793</v>
       </c>
@@ -21852,11 +22013,13 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="2" t="s">
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>793</v>
       </c>
@@ -21878,11 +22041,13 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
-      <c r="L72" s="2" t="s">
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>793</v>
       </c>
@@ -21904,11 +22069,13 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
-      <c r="L73" s="2" t="s">
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>793</v>
       </c>
@@ -21930,11 +22097,13 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
-      <c r="L74" s="2" t="s">
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>793</v>
       </c>
@@ -21956,11 +22125,13 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
-      <c r="L75" s="2" t="s">
+      <c r="L75" s="2"/>
+      <c r="M75" s="2"/>
+      <c r="N75" s="2" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>794</v>
       </c>
@@ -21982,11 +22153,13 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
-      <c r="L76" s="2" t="s">
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>794</v>
       </c>
@@ -22008,11 +22181,13 @@
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
-      <c r="L77" s="2" t="s">
+      <c r="L77" s="2"/>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>794</v>
       </c>
@@ -22034,11 +22209,13 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
-      <c r="L78" s="2" t="s">
+      <c r="L78" s="2"/>
+      <c r="M78" s="2"/>
+      <c r="N78" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>794</v>
       </c>
@@ -22060,11 +22237,13 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
-      <c r="L79" s="2" t="s">
+      <c r="L79" s="2"/>
+      <c r="M79" s="2"/>
+      <c r="N79" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>794</v>
       </c>
@@ -22086,11 +22265,13 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
-      <c r="L80" s="2" t="s">
+      <c r="L80" s="2"/>
+      <c r="M80" s="2"/>
+      <c r="N80" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>794</v>
       </c>
@@ -22112,11 +22293,13 @@
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
-      <c r="L81" s="2" t="s">
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
+      <c r="N81" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>794</v>
       </c>
@@ -22140,11 +22323,13 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
-      <c r="L82" s="2" t="s">
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
+      <c r="N82" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>794</v>
       </c>
@@ -22168,11 +22353,13 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
-      <c r="L83" s="2" t="s">
+      <c r="L83" s="2"/>
+      <c r="M83" s="2"/>
+      <c r="N83" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>794</v>
       </c>
@@ -22196,11 +22383,13 @@
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
-      <c r="L84" s="2" t="s">
+      <c r="L84" s="2"/>
+      <c r="M84" s="2"/>
+      <c r="N84" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>794</v>
       </c>
@@ -22224,11 +22413,13 @@
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
-      <c r="L85" s="2" t="s">
+      <c r="L85" s="2"/>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>795</v>
       </c>
@@ -22250,11 +22441,15 @@
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
-      <c r="L86" s="2" t="s">
+      <c r="L86" s="2"/>
+      <c r="M86" s="2" t="s">
+        <v>2149</v>
+      </c>
+      <c r="N86" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>795</v>
       </c>
@@ -22276,11 +22471,13 @@
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
-      <c r="L87" s="2" t="s">
+      <c r="L87" s="2"/>
+      <c r="M87" s="2"/>
+      <c r="N87" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>795</v>
       </c>
@@ -22302,11 +22499,13 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
-      <c r="L88" s="2" t="s">
+      <c r="L88" s="2"/>
+      <c r="M88" s="2"/>
+      <c r="N88" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>795</v>
       </c>
@@ -22326,13 +22525,17 @@
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
+      <c r="J89" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="K89" s="2"/>
-      <c r="L89" s="2" t="s">
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
+      <c r="N89" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>796</v>
       </c>
@@ -22358,11 +22561,13 @@
         <v>1</v>
       </c>
       <c r="K90" s="2"/>
-      <c r="L90" s="2" t="s">
+      <c r="L90" s="2"/>
+      <c r="M90" s="2"/>
+      <c r="N90" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>796</v>
       </c>
@@ -22386,11 +22591,13 @@
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
-      <c r="L91" s="2" t="s">
+      <c r="L91" s="2"/>
+      <c r="M91" s="2"/>
+      <c r="N91" s="2" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>796</v>
       </c>
@@ -22414,11 +22621,13 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
-      <c r="L92" s="2" t="s">
+      <c r="L92" s="2"/>
+      <c r="M92" s="2"/>
+      <c r="N92" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>796</v>
       </c>
@@ -22441,14 +22650,16 @@
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
-      <c r="K93" s="2" t="s">
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2" t="s">
         <v>2154</v>
       </c>
-      <c r="L93" s="2" t="s">
+      <c r="N93" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>796</v>
       </c>
@@ -22472,11 +22683,13 @@
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
-      <c r="L94" s="2" t="s">
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
+      <c r="N94" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>796</v>
       </c>
@@ -22498,11 +22711,13 @@
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
-      <c r="L95" s="2" t="s">
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
+      <c r="N95" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>798</v>
       </c>
@@ -22526,11 +22741,13 @@
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
-      <c r="L96" s="2" t="s">
+      <c r="L96" s="2"/>
+      <c r="M96" s="2"/>
+      <c r="N96" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>798</v>
       </c>
@@ -22554,11 +22771,13 @@
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
-      <c r="L97" s="2" t="s">
+      <c r="L97" s="2"/>
+      <c r="M97" s="2"/>
+      <c r="N97" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>798</v>
       </c>
@@ -22582,11 +22801,13 @@
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
-      <c r="L98" s="2" t="s">
+      <c r="L98" s="2"/>
+      <c r="M98" s="2"/>
+      <c r="N98" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>798</v>
       </c>
@@ -22610,11 +22831,13 @@
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
-      <c r="L99" s="2" t="s">
+      <c r="L99" s="2"/>
+      <c r="M99" s="2"/>
+      <c r="N99" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>798</v>
       </c>
@@ -22638,11 +22861,13 @@
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
-      <c r="L100" s="2" t="s">
+      <c r="L100" s="2"/>
+      <c r="M100" s="2"/>
+      <c r="N100" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>798</v>
       </c>
@@ -22666,11 +22891,13 @@
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
-      <c r="L101" s="2" t="s">
+      <c r="L101" s="2"/>
+      <c r="M101" s="2"/>
+      <c r="N101" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>798</v>
       </c>
@@ -22694,11 +22921,13 @@
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
-      <c r="L102" s="2" t="s">
+      <c r="L102" s="2"/>
+      <c r="M102" s="2"/>
+      <c r="N102" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>798</v>
       </c>
@@ -22722,11 +22951,13 @@
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
-      <c r="L103" s="2" t="s">
+      <c r="L103" s="2"/>
+      <c r="M103" s="2"/>
+      <c r="N103" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>798</v>
       </c>
@@ -22750,11 +22981,13 @@
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
-      <c r="L104" s="2" t="s">
+      <c r="L104" s="2"/>
+      <c r="M104" s="2"/>
+      <c r="N104" s="2" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>798</v>
       </c>
@@ -22778,11 +23011,13 @@
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
-      <c r="L105" s="2" t="s">
+      <c r="L105" s="2"/>
+      <c r="M105" s="2"/>
+      <c r="N105" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>798</v>
       </c>
@@ -22808,11 +23043,13 @@
       </c>
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
-      <c r="L106" s="2" t="s">
+      <c r="L106" s="2"/>
+      <c r="M106" s="2"/>
+      <c r="N106" s="2" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>798</v>
       </c>
@@ -22836,11 +23073,13 @@
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
       <c r="K107" s="2"/>
-      <c r="L107" s="2" t="s">
+      <c r="L107" s="2"/>
+      <c r="M107" s="2"/>
+      <c r="N107" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>798</v>
       </c>
@@ -22864,11 +23103,13 @@
       <c r="I108" s="2"/>
       <c r="J108" s="2"/>
       <c r="K108" s="2"/>
-      <c r="L108" s="2" t="s">
+      <c r="L108" s="2"/>
+      <c r="M108" s="2"/>
+      <c r="N108" s="2" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>798</v>
       </c>
@@ -22894,11 +23135,13 @@
       </c>
       <c r="J109" s="2"/>
       <c r="K109" s="2"/>
-      <c r="L109" s="2" t="s">
+      <c r="L109" s="2"/>
+      <c r="M109" s="2"/>
+      <c r="N109" s="2" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>798</v>
       </c>
@@ -22922,11 +23165,13 @@
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
       <c r="K110" s="2"/>
-      <c r="L110" s="2" t="s">
+      <c r="L110" s="2"/>
+      <c r="M110" s="2"/>
+      <c r="N110" s="2" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>798</v>
       </c>
@@ -22950,11 +23195,13 @@
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
       <c r="K111" s="2"/>
-      <c r="L111" s="2" t="s">
+      <c r="L111" s="2"/>
+      <c r="M111" s="2"/>
+      <c r="N111" s="2" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>798</v>
       </c>
@@ -22978,11 +23225,13 @@
       <c r="I112" s="2"/>
       <c r="J112" s="2"/>
       <c r="K112" s="2"/>
-      <c r="L112" s="2" t="s">
+      <c r="L112" s="2"/>
+      <c r="M112" s="2"/>
+      <c r="N112" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>798</v>
       </c>
@@ -23006,11 +23255,13 @@
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
       <c r="K113" s="2"/>
-      <c r="L113" s="2" t="s">
+      <c r="L113" s="2"/>
+      <c r="M113" s="2"/>
+      <c r="N113" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>800</v>
       </c>
@@ -23032,11 +23283,13 @@
       <c r="I114" s="2"/>
       <c r="J114" s="2"/>
       <c r="K114" s="2"/>
-      <c r="L114" s="2" t="s">
+      <c r="L114" s="2"/>
+      <c r="M114" s="2"/>
+      <c r="N114" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>800</v>
       </c>
@@ -23058,11 +23311,13 @@
       <c r="I115" s="2"/>
       <c r="J115" s="2"/>
       <c r="K115" s="2"/>
-      <c r="L115" s="2" t="s">
+      <c r="L115" s="2"/>
+      <c r="M115" s="2"/>
+      <c r="N115" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>800</v>
       </c>
@@ -23084,11 +23339,13 @@
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
       <c r="K116" s="2"/>
-      <c r="L116" s="2" t="s">
+      <c r="L116" s="2"/>
+      <c r="M116" s="2"/>
+      <c r="N116" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>800</v>
       </c>
@@ -23110,11 +23367,13 @@
       <c r="I117" s="2"/>
       <c r="J117" s="2"/>
       <c r="K117" s="2"/>
-      <c r="L117" s="2" t="s">
+      <c r="L117" s="2"/>
+      <c r="M117" s="2"/>
+      <c r="N117" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>800</v>
       </c>
@@ -23136,11 +23395,13 @@
       <c r="I118" s="2"/>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
-      <c r="L118" s="2" t="s">
+      <c r="L118" s="2"/>
+      <c r="M118" s="2"/>
+      <c r="N118" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>800</v>
       </c>
@@ -23162,11 +23423,13 @@
       <c r="I119" s="2"/>
       <c r="J119" s="2"/>
       <c r="K119" s="2"/>
-      <c r="L119" s="2" t="s">
+      <c r="L119" s="2"/>
+      <c r="M119" s="2"/>
+      <c r="N119" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>801</v>
       </c>
@@ -23188,11 +23451,13 @@
       <c r="I120" s="2"/>
       <c r="J120" s="2"/>
       <c r="K120" s="2"/>
-      <c r="L120" s="2" t="s">
+      <c r="L120" s="2"/>
+      <c r="M120" s="2"/>
+      <c r="N120" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>801</v>
       </c>
@@ -23214,11 +23479,13 @@
       <c r="I121" s="2"/>
       <c r="J121" s="2"/>
       <c r="K121" s="2"/>
-      <c r="L121" s="2" t="s">
+      <c r="L121" s="2"/>
+      <c r="M121" s="2"/>
+      <c r="N121" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>801</v>
       </c>
@@ -23240,11 +23507,13 @@
       <c r="I122" s="2"/>
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
-      <c r="L122" s="2" t="s">
+      <c r="L122" s="2"/>
+      <c r="M122" s="2"/>
+      <c r="N122" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>801</v>
       </c>
@@ -23266,11 +23535,13 @@
       <c r="I123" s="2"/>
       <c r="J123" s="2"/>
       <c r="K123" s="2"/>
-      <c r="L123" s="2" t="s">
+      <c r="L123" s="2"/>
+      <c r="M123" s="2"/>
+      <c r="N123" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>801</v>
       </c>
@@ -23292,11 +23563,13 @@
       <c r="I124" s="2"/>
       <c r="J124" s="2"/>
       <c r="K124" s="2"/>
-      <c r="L124" s="2" t="s">
+      <c r="L124" s="2"/>
+      <c r="M124" s="2"/>
+      <c r="N124" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>801</v>
       </c>
@@ -23318,11 +23591,13 @@
       <c r="I125" s="2"/>
       <c r="J125" s="2"/>
       <c r="K125" s="2"/>
-      <c r="L125" s="2" t="s">
+      <c r="L125" s="2"/>
+      <c r="M125" s="2"/>
+      <c r="N125" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>801</v>
       </c>
@@ -23344,11 +23619,13 @@
       <c r="I126" s="2"/>
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
-      <c r="L126" s="2" t="s">
+      <c r="L126" s="2"/>
+      <c r="M126" s="2"/>
+      <c r="N126" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>801</v>
       </c>
@@ -23370,11 +23647,13 @@
       <c r="I127" s="2"/>
       <c r="J127" s="2"/>
       <c r="K127" s="2"/>
-      <c r="L127" s="2" t="s">
+      <c r="L127" s="2"/>
+      <c r="M127" s="2"/>
+      <c r="N127" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>801</v>
       </c>
@@ -23396,11 +23675,13 @@
       <c r="I128" s="2"/>
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
-      <c r="L128" s="2" t="s">
+      <c r="L128" s="2"/>
+      <c r="M128" s="2"/>
+      <c r="N128" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>801</v>
       </c>
@@ -23422,11 +23703,13 @@
       <c r="I129" s="2"/>
       <c r="J129" s="2"/>
       <c r="K129" s="2"/>
-      <c r="L129" s="2" t="s">
+      <c r="L129" s="2"/>
+      <c r="M129" s="2"/>
+      <c r="N129" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>155</v>
       </c>
@@ -23450,11 +23733,13 @@
       <c r="I130" s="2"/>
       <c r="J130" s="2"/>
       <c r="K130" s="2"/>
-      <c r="L130" s="2" t="s">
+      <c r="L130" s="2"/>
+      <c r="M130" s="2"/>
+      <c r="N130" s="2" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>155</v>
       </c>
@@ -23478,11 +23763,13 @@
       <c r="I131" s="2"/>
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
-      <c r="L131" s="2" t="s">
+      <c r="L131" s="2"/>
+      <c r="M131" s="2"/>
+      <c r="N131" s="2" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>155</v>
       </c>
@@ -23506,11 +23793,13 @@
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
       <c r="K132" s="2"/>
-      <c r="L132" s="2" t="s">
+      <c r="L132" s="2"/>
+      <c r="M132" s="2"/>
+      <c r="N132" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>155</v>
       </c>
@@ -23534,11 +23823,13 @@
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
       <c r="K133" s="2"/>
-      <c r="L133" s="2" t="s">
+      <c r="L133" s="2"/>
+      <c r="M133" s="2"/>
+      <c r="N133" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>155</v>
       </c>
@@ -23562,11 +23853,13 @@
       <c r="I134" s="2"/>
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
-      <c r="L134" s="2" t="s">
+      <c r="L134" s="2"/>
+      <c r="M134" s="2"/>
+      <c r="N134" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>155</v>
       </c>
@@ -23590,11 +23883,13 @@
       <c r="I135" s="2"/>
       <c r="J135" s="2"/>
       <c r="K135" s="2"/>
-      <c r="L135" s="2" t="s">
+      <c r="L135" s="2"/>
+      <c r="M135" s="2"/>
+      <c r="N135" s="2" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>155</v>
       </c>
@@ -23618,11 +23913,13 @@
       <c r="I136" s="2"/>
       <c r="J136" s="2"/>
       <c r="K136" s="2"/>
-      <c r="L136" s="2" t="s">
+      <c r="L136" s="2"/>
+      <c r="M136" s="2"/>
+      <c r="N136" s="2" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>155</v>
       </c>
@@ -23646,11 +23943,13 @@
       <c r="I137" s="2"/>
       <c r="J137" s="2"/>
       <c r="K137" s="2"/>
-      <c r="L137" s="2" t="s">
+      <c r="L137" s="2"/>
+      <c r="M137" s="2"/>
+      <c r="N137" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>155</v>
       </c>
@@ -23674,11 +23973,13 @@
       <c r="I138" s="2"/>
       <c r="J138" s="2"/>
       <c r="K138" s="2"/>
-      <c r="L138" s="2" t="s">
+      <c r="L138" s="2"/>
+      <c r="M138" s="2"/>
+      <c r="N138" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>155</v>
       </c>
@@ -23702,11 +24003,13 @@
       <c r="I139" s="2"/>
       <c r="J139" s="2"/>
       <c r="K139" s="2"/>
-      <c r="L139" s="2" t="s">
+      <c r="L139" s="2"/>
+      <c r="M139" s="2"/>
+      <c r="N139" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>155</v>
       </c>
@@ -23730,11 +24033,13 @@
       <c r="I140" s="2"/>
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
-      <c r="L140" s="2" t="s">
+      <c r="L140" s="2"/>
+      <c r="M140" s="2"/>
+      <c r="N140" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>155</v>
       </c>
@@ -23758,11 +24063,13 @@
       <c r="I141" s="2"/>
       <c r="J141" s="2"/>
       <c r="K141" s="2"/>
-      <c r="L141" s="2" t="s">
+      <c r="L141" s="2"/>
+      <c r="M141" s="2"/>
+      <c r="N141" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>155</v>
       </c>
@@ -23786,11 +24093,13 @@
       <c r="I142" s="2"/>
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
-      <c r="L142" s="2" t="s">
+      <c r="L142" s="2"/>
+      <c r="M142" s="2"/>
+      <c r="N142" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>155</v>
       </c>
@@ -23814,11 +24123,13 @@
       <c r="I143" s="2"/>
       <c r="J143" s="2"/>
       <c r="K143" s="2"/>
-      <c r="L143" s="2" t="s">
+      <c r="L143" s="2"/>
+      <c r="M143" s="2"/>
+      <c r="N143" s="2" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>155</v>
       </c>
@@ -23842,11 +24153,13 @@
       <c r="I144" s="2"/>
       <c r="J144" s="2"/>
       <c r="K144" s="2"/>
-      <c r="L144" s="2" t="s">
+      <c r="L144" s="2"/>
+      <c r="M144" s="2"/>
+      <c r="N144" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>155</v>
       </c>
@@ -23870,11 +24183,13 @@
       <c r="I145" s="2"/>
       <c r="J145" s="2"/>
       <c r="K145" s="2"/>
-      <c r="L145" s="2" t="s">
+      <c r="L145" s="2"/>
+      <c r="M145" s="2"/>
+      <c r="N145" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>802</v>
       </c>
@@ -23898,11 +24213,13 @@
       </c>
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
-      <c r="L146" s="2" t="s">
+      <c r="L146" s="2"/>
+      <c r="M146" s="2"/>
+      <c r="N146" s="2" t="s">
         <v>977</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>802</v>
       </c>
@@ -23924,11 +24241,13 @@
       <c r="I147" s="2"/>
       <c r="J147" s="2"/>
       <c r="K147" s="2"/>
-      <c r="L147" s="2" t="s">
+      <c r="L147" s="2"/>
+      <c r="M147" s="2"/>
+      <c r="N147" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>802</v>
       </c>
@@ -23950,11 +24269,13 @@
       <c r="I148" s="2"/>
       <c r="J148" s="2"/>
       <c r="K148" s="2"/>
-      <c r="L148" s="2" t="s">
+      <c r="L148" s="2"/>
+      <c r="M148" s="2"/>
+      <c r="N148" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>802</v>
       </c>
@@ -23976,11 +24297,13 @@
       <c r="I149" s="2"/>
       <c r="J149" s="2"/>
       <c r="K149" s="2"/>
-      <c r="L149" s="2" t="s">
+      <c r="L149" s="2"/>
+      <c r="M149" s="2"/>
+      <c r="N149" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>802</v>
       </c>
@@ -24002,11 +24325,13 @@
       <c r="I150" s="2"/>
       <c r="J150" s="2"/>
       <c r="K150" s="2"/>
-      <c r="L150" s="2" t="s">
+      <c r="L150" s="2"/>
+      <c r="M150" s="2"/>
+      <c r="N150" s="2" t="s">
         <v>982</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>802</v>
       </c>
@@ -24028,11 +24353,13 @@
       <c r="I151" s="2"/>
       <c r="J151" s="2"/>
       <c r="K151" s="2"/>
-      <c r="L151" s="2" t="s">
+      <c r="L151" s="2"/>
+      <c r="M151" s="2"/>
+      <c r="N151" s="2" t="s">
         <v>982</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>802</v>
       </c>
@@ -24056,11 +24383,13 @@
       </c>
       <c r="J152" s="2"/>
       <c r="K152" s="2"/>
-      <c r="L152" s="2" t="s">
+      <c r="L152" s="2"/>
+      <c r="M152" s="2"/>
+      <c r="N152" s="2" t="s">
         <v>985</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>802</v>
       </c>
@@ -24082,11 +24411,13 @@
       <c r="I153" s="2"/>
       <c r="J153" s="2"/>
       <c r="K153" s="2"/>
-      <c r="L153" s="2" t="s">
+      <c r="L153" s="2"/>
+      <c r="M153" s="2"/>
+      <c r="N153" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>802</v>
       </c>
@@ -24108,11 +24439,13 @@
       <c r="I154" s="2"/>
       <c r="J154" s="2"/>
       <c r="K154" s="2"/>
-      <c r="L154" s="2" t="s">
+      <c r="L154" s="2"/>
+      <c r="M154" s="2"/>
+      <c r="N154" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>802</v>
       </c>
@@ -24134,11 +24467,13 @@
       <c r="I155" s="2"/>
       <c r="J155" s="2"/>
       <c r="K155" s="2"/>
-      <c r="L155" s="2" t="s">
+      <c r="L155" s="2"/>
+      <c r="M155" s="2"/>
+      <c r="N155" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>802</v>
       </c>
@@ -24160,11 +24495,13 @@
       <c r="I156" s="2"/>
       <c r="J156" s="2"/>
       <c r="K156" s="2"/>
-      <c r="L156" s="2" t="s">
+      <c r="L156" s="2"/>
+      <c r="M156" s="2"/>
+      <c r="N156" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>802</v>
       </c>
@@ -24186,11 +24523,13 @@
       <c r="I157" s="2"/>
       <c r="J157" s="2"/>
       <c r="K157" s="2"/>
-      <c r="L157" s="2" t="s">
+      <c r="L157" s="2"/>
+      <c r="M157" s="2"/>
+      <c r="N157" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>802</v>
       </c>
@@ -24212,11 +24551,13 @@
       <c r="I158" s="2"/>
       <c r="J158" s="2"/>
       <c r="K158" s="2"/>
-      <c r="L158" s="2" t="s">
+      <c r="L158" s="2"/>
+      <c r="M158" s="2"/>
+      <c r="N158" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>802</v>
       </c>
@@ -24238,11 +24579,13 @@
       <c r="I159" s="2"/>
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
-      <c r="L159" s="2" t="s">
+      <c r="L159" s="2"/>
+      <c r="M159" s="2"/>
+      <c r="N159" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>802</v>
       </c>
@@ -24264,11 +24607,13 @@
       <c r="I160" s="2"/>
       <c r="J160" s="2"/>
       <c r="K160" s="2"/>
-      <c r="L160" s="2" t="s">
+      <c r="L160" s="2"/>
+      <c r="M160" s="2"/>
+      <c r="N160" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>802</v>
       </c>
@@ -24290,11 +24635,13 @@
       <c r="I161" s="2"/>
       <c r="J161" s="2"/>
       <c r="K161" s="2"/>
-      <c r="L161" s="2" t="s">
+      <c r="L161" s="2"/>
+      <c r="M161" s="2"/>
+      <c r="N161" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>802</v>
       </c>
@@ -24316,11 +24663,13 @@
       <c r="I162" s="2"/>
       <c r="J162" s="2"/>
       <c r="K162" s="2"/>
-      <c r="L162" s="2" t="s">
+      <c r="L162" s="2"/>
+      <c r="M162" s="2"/>
+      <c r="N162" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>802</v>
       </c>
@@ -24342,11 +24691,13 @@
       <c r="I163" s="2"/>
       <c r="J163" s="2"/>
       <c r="K163" s="2"/>
-      <c r="L163" s="2" t="s">
+      <c r="L163" s="2"/>
+      <c r="M163" s="2"/>
+      <c r="N163" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>802</v>
       </c>
@@ -24368,11 +24719,13 @@
       <c r="I164" s="2"/>
       <c r="J164" s="2"/>
       <c r="K164" s="2"/>
-      <c r="L164" s="2" t="s">
+      <c r="L164" s="2"/>
+      <c r="M164" s="2"/>
+      <c r="N164" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>803</v>
       </c>
@@ -24394,11 +24747,13 @@
       <c r="I165" s="2"/>
       <c r="J165" s="2"/>
       <c r="K165" s="2"/>
-      <c r="L165" s="2" t="s">
+      <c r="L165" s="2"/>
+      <c r="M165" s="2"/>
+      <c r="N165" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>803</v>
       </c>
@@ -24420,11 +24775,13 @@
       <c r="I166" s="2"/>
       <c r="J166" s="2"/>
       <c r="K166" s="2"/>
-      <c r="L166" s="2" t="s">
+      <c r="L166" s="2"/>
+      <c r="M166" s="2"/>
+      <c r="N166" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>803</v>
       </c>
@@ -24446,11 +24803,13 @@
       <c r="I167" s="2"/>
       <c r="J167" s="2"/>
       <c r="K167" s="2"/>
-      <c r="L167" s="2" t="s">
+      <c r="L167" s="2"/>
+      <c r="M167" s="2"/>
+      <c r="N167" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>803</v>
       </c>
@@ -24472,11 +24831,13 @@
       <c r="I168" s="2"/>
       <c r="J168" s="2"/>
       <c r="K168" s="2"/>
-      <c r="L168" s="2" t="s">
+      <c r="L168" s="2"/>
+      <c r="M168" s="2"/>
+      <c r="N168" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>803</v>
       </c>
@@ -24498,11 +24859,13 @@
       <c r="I169" s="2"/>
       <c r="J169" s="2"/>
       <c r="K169" s="2"/>
-      <c r="L169" s="2" t="s">
+      <c r="L169" s="2"/>
+      <c r="M169" s="2"/>
+      <c r="N169" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>803</v>
       </c>
@@ -24524,11 +24887,13 @@
       <c r="I170" s="2"/>
       <c r="J170" s="2"/>
       <c r="K170" s="2"/>
-      <c r="L170" s="2" t="s">
+      <c r="L170" s="2"/>
+      <c r="M170" s="2"/>
+      <c r="N170" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>805</v>
       </c>
@@ -24550,11 +24915,13 @@
       <c r="I171" s="2"/>
       <c r="J171" s="2"/>
       <c r="K171" s="2"/>
-      <c r="L171" s="2" t="s">
+      <c r="L171" s="2"/>
+      <c r="M171" s="2"/>
+      <c r="N171" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>805</v>
       </c>
@@ -24576,11 +24943,13 @@
       <c r="I172" s="2"/>
       <c r="J172" s="2"/>
       <c r="K172" s="2"/>
-      <c r="L172" s="2" t="s">
+      <c r="L172" s="2"/>
+      <c r="M172" s="2"/>
+      <c r="N172" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>805</v>
       </c>
@@ -24604,11 +24973,13 @@
       </c>
       <c r="J173" s="2"/>
       <c r="K173" s="2"/>
-      <c r="L173" s="2" t="s">
+      <c r="L173" s="2"/>
+      <c r="M173" s="2"/>
+      <c r="N173" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>805</v>
       </c>
@@ -24630,11 +25001,13 @@
       <c r="I174" s="2"/>
       <c r="J174" s="2"/>
       <c r="K174" s="2"/>
-      <c r="L174" s="2" t="s">
+      <c r="L174" s="2"/>
+      <c r="M174" s="2"/>
+      <c r="N174" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>806</v>
       </c>
@@ -24658,11 +25031,13 @@
       <c r="I175" s="2"/>
       <c r="J175" s="2"/>
       <c r="K175" s="2"/>
-      <c r="L175" s="2" t="s">
+      <c r="L175" s="2"/>
+      <c r="M175" s="2"/>
+      <c r="N175" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>806</v>
       </c>
@@ -24686,11 +25061,13 @@
       <c r="I176" s="2"/>
       <c r="J176" s="2"/>
       <c r="K176" s="2"/>
-      <c r="L176" s="2" t="s">
+      <c r="L176" s="2"/>
+      <c r="M176" s="2"/>
+      <c r="N176" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>806</v>
       </c>
@@ -24714,11 +25091,13 @@
       <c r="I177" s="2"/>
       <c r="J177" s="2"/>
       <c r="K177" s="2"/>
-      <c r="L177" s="2" t="s">
+      <c r="L177" s="2"/>
+      <c r="M177" s="2"/>
+      <c r="N177" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>806</v>
       </c>
@@ -24742,11 +25121,13 @@
       <c r="I178" s="2"/>
       <c r="J178" s="2"/>
       <c r="K178" s="2"/>
-      <c r="L178" s="2" t="s">
+      <c r="L178" s="2"/>
+      <c r="M178" s="2"/>
+      <c r="N178" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>806</v>
       </c>
@@ -24770,11 +25151,13 @@
       <c r="I179" s="2"/>
       <c r="J179" s="2"/>
       <c r="K179" s="2"/>
-      <c r="L179" s="2" t="s">
+      <c r="L179" s="2"/>
+      <c r="M179" s="2"/>
+      <c r="N179" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>806</v>
       </c>
@@ -24798,11 +25181,13 @@
       <c r="I180" s="2"/>
       <c r="J180" s="2"/>
       <c r="K180" s="2"/>
-      <c r="L180" s="2" t="s">
+      <c r="L180" s="2"/>
+      <c r="M180" s="2"/>
+      <c r="N180" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>806</v>
       </c>
@@ -24826,11 +25211,13 @@
       <c r="I181" s="2"/>
       <c r="J181" s="2"/>
       <c r="K181" s="2"/>
-      <c r="L181" s="2" t="s">
+      <c r="L181" s="2"/>
+      <c r="M181" s="2"/>
+      <c r="N181" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>806</v>
       </c>
@@ -24854,11 +25241,13 @@
       <c r="I182" s="2"/>
       <c r="J182" s="2"/>
       <c r="K182" s="2"/>
-      <c r="L182" s="2" t="s">
+      <c r="L182" s="2"/>
+      <c r="M182" s="2"/>
+      <c r="N182" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>806</v>
       </c>
@@ -24882,11 +25271,13 @@
       <c r="I183" s="2"/>
       <c r="J183" s="2"/>
       <c r="K183" s="2"/>
-      <c r="L183" s="2" t="s">
+      <c r="L183" s="2"/>
+      <c r="M183" s="2"/>
+      <c r="N183" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>806</v>
       </c>
@@ -24910,11 +25301,13 @@
       <c r="I184" s="2"/>
       <c r="J184" s="2"/>
       <c r="K184" s="2"/>
-      <c r="L184" s="2" t="s">
+      <c r="L184" s="2"/>
+      <c r="M184" s="2"/>
+      <c r="N184" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>806</v>
       </c>
@@ -24938,11 +25331,13 @@
       <c r="I185" s="2"/>
       <c r="J185" s="2"/>
       <c r="K185" s="2"/>
-      <c r="L185" s="2" t="s">
+      <c r="L185" s="2"/>
+      <c r="M185" s="2"/>
+      <c r="N185" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>806</v>
       </c>
@@ -24966,11 +25361,13 @@
       <c r="I186" s="2"/>
       <c r="J186" s="2"/>
       <c r="K186" s="2"/>
-      <c r="L186" s="2" t="s">
+      <c r="L186" s="2"/>
+      <c r="M186" s="2"/>
+      <c r="N186" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>806</v>
       </c>
@@ -24994,11 +25391,13 @@
       <c r="I187" s="2"/>
       <c r="J187" s="2"/>
       <c r="K187" s="2"/>
-      <c r="L187" s="2" t="s">
+      <c r="L187" s="2"/>
+      <c r="M187" s="2"/>
+      <c r="N187" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>806</v>
       </c>
@@ -25022,11 +25421,13 @@
       <c r="I188" s="2"/>
       <c r="J188" s="2"/>
       <c r="K188" s="2"/>
-      <c r="L188" s="2" t="s">
+      <c r="L188" s="2"/>
+      <c r="M188" s="2"/>
+      <c r="N188" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>806</v>
       </c>
@@ -25050,11 +25451,13 @@
       <c r="I189" s="2"/>
       <c r="J189" s="2"/>
       <c r="K189" s="2"/>
-      <c r="L189" s="2" t="s">
+      <c r="L189" s="2"/>
+      <c r="M189" s="2"/>
+      <c r="N189" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>806</v>
       </c>
@@ -25078,11 +25481,13 @@
       <c r="I190" s="2"/>
       <c r="J190" s="2"/>
       <c r="K190" s="2"/>
-      <c r="L190" s="2" t="s">
+      <c r="L190" s="2"/>
+      <c r="M190" s="2"/>
+      <c r="N190" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>806</v>
       </c>
@@ -25106,11 +25511,13 @@
       <c r="I191" s="2"/>
       <c r="J191" s="2"/>
       <c r="K191" s="2"/>
-      <c r="L191" s="2" t="s">
+      <c r="L191" s="2"/>
+      <c r="M191" s="2"/>
+      <c r="N191" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>806</v>
       </c>
@@ -25134,11 +25541,13 @@
       <c r="I192" s="2"/>
       <c r="J192" s="2"/>
       <c r="K192" s="2"/>
-      <c r="L192" s="2" t="s">
+      <c r="L192" s="2"/>
+      <c r="M192" s="2"/>
+      <c r="N192" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>806</v>
       </c>
@@ -25162,11 +25571,13 @@
       <c r="I193" s="2"/>
       <c r="J193" s="2"/>
       <c r="K193" s="2"/>
-      <c r="L193" s="2" t="s">
+      <c r="L193" s="2"/>
+      <c r="M193" s="2"/>
+      <c r="N193" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>806</v>
       </c>
@@ -25190,11 +25601,13 @@
       <c r="I194" s="2"/>
       <c r="J194" s="2"/>
       <c r="K194" s="2"/>
-      <c r="L194" s="2" t="s">
+      <c r="L194" s="2"/>
+      <c r="M194" s="2"/>
+      <c r="N194" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>806</v>
       </c>
@@ -25218,11 +25631,13 @@
       <c r="I195" s="2"/>
       <c r="J195" s="2"/>
       <c r="K195" s="2"/>
-      <c r="L195" s="2" t="s">
+      <c r="L195" s="2"/>
+      <c r="M195" s="2"/>
+      <c r="N195" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>799</v>
       </c>
@@ -25246,11 +25661,13 @@
       <c r="I196" s="2"/>
       <c r="J196" s="2"/>
       <c r="K196" s="2"/>
-      <c r="L196" s="2" t="s">
+      <c r="L196" s="2"/>
+      <c r="M196" s="2"/>
+      <c r="N196" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>799</v>
       </c>
@@ -25274,11 +25691,13 @@
       <c r="I197" s="2"/>
       <c r="J197" s="2"/>
       <c r="K197" s="2"/>
-      <c r="L197" s="2" t="s">
+      <c r="L197" s="2"/>
+      <c r="M197" s="2"/>
+      <c r="N197" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>799</v>
       </c>
@@ -25302,11 +25721,13 @@
       <c r="I198" s="2"/>
       <c r="J198" s="2"/>
       <c r="K198" s="2"/>
-      <c r="L198" s="2" t="s">
+      <c r="L198" s="2"/>
+      <c r="M198" s="2"/>
+      <c r="N198" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>799</v>
       </c>
@@ -25330,11 +25751,13 @@
       <c r="I199" s="2"/>
       <c r="J199" s="2"/>
       <c r="K199" s="2"/>
-      <c r="L199" s="2" t="s">
+      <c r="L199" s="2"/>
+      <c r="M199" s="2"/>
+      <c r="N199" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>799</v>
       </c>
@@ -25360,11 +25783,13 @@
       </c>
       <c r="J200" s="2"/>
       <c r="K200" s="2"/>
-      <c r="L200" s="2" t="s">
+      <c r="L200" s="2"/>
+      <c r="M200" s="2"/>
+      <c r="N200" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>799</v>
       </c>
@@ -25388,11 +25813,13 @@
       <c r="I201" s="2"/>
       <c r="J201" s="2"/>
       <c r="K201" s="2"/>
-      <c r="L201" s="2" t="s">
+      <c r="L201" s="2"/>
+      <c r="M201" s="2"/>
+      <c r="N201" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>799</v>
       </c>
@@ -25416,11 +25843,13 @@
       <c r="I202" s="2"/>
       <c r="J202" s="2"/>
       <c r="K202" s="2"/>
-      <c r="L202" s="2" t="s">
+      <c r="L202" s="2"/>
+      <c r="M202" s="2"/>
+      <c r="N202" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>799</v>
       </c>
@@ -25444,11 +25873,13 @@
       <c r="I203" s="2"/>
       <c r="J203" s="2"/>
       <c r="K203" s="2"/>
-      <c r="L203" s="2" t="s">
+      <c r="L203" s="2"/>
+      <c r="M203" s="2"/>
+      <c r="N203" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>799</v>
       </c>
@@ -25472,11 +25903,13 @@
       <c r="I204" s="2"/>
       <c r="J204" s="2"/>
       <c r="K204" s="2"/>
-      <c r="L204" s="2" t="s">
+      <c r="L204" s="2"/>
+      <c r="M204" s="2"/>
+      <c r="N204" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>799</v>
       </c>
@@ -25500,11 +25933,13 @@
       <c r="I205" s="2"/>
       <c r="J205" s="2"/>
       <c r="K205" s="2"/>
-      <c r="L205" s="2" t="s">
+      <c r="L205" s="2"/>
+      <c r="M205" s="2"/>
+      <c r="N205" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>799</v>
       </c>
@@ -25528,11 +25963,13 @@
       <c r="I206" s="2"/>
       <c r="J206" s="2"/>
       <c r="K206" s="2"/>
-      <c r="L206" s="2" t="s">
+      <c r="L206" s="2"/>
+      <c r="M206" s="2"/>
+      <c r="N206" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>799</v>
       </c>
@@ -25556,11 +25993,13 @@
       <c r="I207" s="2"/>
       <c r="J207" s="2"/>
       <c r="K207" s="2"/>
-      <c r="L207" s="2" t="s">
+      <c r="L207" s="2"/>
+      <c r="M207" s="2"/>
+      <c r="N207" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>799</v>
       </c>
@@ -25584,7 +26023,9 @@
       <c r="I208" s="2"/>
       <c r="J208" s="2"/>
       <c r="K208" s="2"/>
-      <c r="L208" s="2" t="s">
+      <c r="L208" s="2"/>
+      <c r="M208" s="2"/>
+      <c r="N208" s="2" t="s">
         <v>342</v>
       </c>
     </row>
@@ -38933,7 +39374,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{621D4411-E9D3-49C0-9822-D1D8BB2C515A}">
-  <dimension ref="A1:K281"/>
+  <dimension ref="A1:L281"/>
   <sheetFormatPr defaultColWidth="85.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -38942,12 +39383,13 @@
     <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -38973,16 +39415,19 @@
         <v>2145</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>2156</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>792</v>
       </c>
@@ -39003,15 +39448,16 @@
       <c r="H2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2"/>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1916</v>
       </c>
@@ -39028,15 +39474,18 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1919</v>
       </c>
@@ -39055,15 +39504,16 @@
         <v>1</v>
       </c>
       <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1477</v>
       </c>
@@ -39080,15 +39530,16 @@
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1921</v>
       </c>
@@ -39109,15 +39560,16 @@
       <c r="H6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1318</v>
       </c>
@@ -39138,15 +39590,16 @@
       <c r="H7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="2"/>
+      <c r="J7" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>1922</v>
       </c>
@@ -39163,15 +39616,16 @@
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="2"/>
+      <c r="J8" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1924</v>
       </c>
@@ -39192,15 +39646,16 @@
       <c r="H9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="2"/>
+      <c r="J9" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>1544</v>
       </c>
@@ -39217,15 +39672,16 @@
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="2"/>
+      <c r="J10" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>1459</v>
       </c>
@@ -39244,15 +39700,16 @@
         <v>1</v>
       </c>
       <c r="H11" s="2"/>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="2"/>
+      <c r="J11" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>1925</v>
       </c>
@@ -39271,17 +39728,18 @@
         <v>1</v>
       </c>
       <c r="H12" s="2"/>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="2"/>
+      <c r="J12" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>1395</v>
       </c>
@@ -39300,15 +39758,16 @@
         <v>1</v>
       </c>
       <c r="H13" s="2"/>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="2"/>
+      <c r="J13" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>1926</v>
       </c>
@@ -39327,15 +39786,16 @@
         <v>1</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="2"/>
+      <c r="J14" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>1462</v>
       </c>
@@ -39356,15 +39816,16 @@
       <c r="H15" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="2"/>
+      <c r="J15" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>1597</v>
       </c>
@@ -39381,15 +39842,16 @@
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="2"/>
+      <c r="J16" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>1298</v>
       </c>
@@ -39406,15 +39868,16 @@
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="2"/>
+      <c r="J17" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>1371</v>
       </c>
@@ -39431,15 +39894,16 @@
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="2"/>
+      <c r="J18" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>1927</v>
       </c>
@@ -39460,17 +39924,18 @@
       <c r="H19" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="2"/>
+      <c r="J19" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>1928</v>
       </c>
@@ -39487,15 +39952,16 @@
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="2"/>
+      <c r="J20" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="K20" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>1930</v>
       </c>
@@ -39516,17 +39982,18 @@
       <c r="H21" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" s="2"/>
+      <c r="J21" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>1702</v>
       </c>
@@ -39545,15 +40012,16 @@
       <c r="H22" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I22" s="2"/>
+      <c r="J22" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>1931</v>
       </c>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>1402</v>
       </c>
@@ -39574,15 +40042,16 @@
       <c r="H23" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="I23" s="2"/>
+      <c r="J23" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="K23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>1336</v>
       </c>
@@ -39599,15 +40068,16 @@
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-      <c r="I24" s="2" t="s">
+      <c r="I24" s="2"/>
+      <c r="J24" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>1365</v>
       </c>
@@ -39626,15 +40096,16 @@
         <v>1</v>
       </c>
       <c r="H25" s="2"/>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="2"/>
+      <c r="J25" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="K25" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>1314</v>
       </c>
@@ -39651,15 +40122,18 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="2" t="s">
+      <c r="I26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="K26" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>1932</v>
       </c>
@@ -39680,15 +40154,16 @@
       <c r="H27" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="I27" s="2"/>
+      <c r="J27" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="K27" s="2" t="s">
         <v>1933</v>
       </c>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>1934</v>
       </c>
@@ -39709,15 +40184,16 @@
       <c r="H28" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="I28" s="2"/>
+      <c r="J28" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="K28" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>1935</v>
       </c>
@@ -39734,15 +40210,16 @@
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-      <c r="I29" s="2" t="s">
+      <c r="I29" s="2"/>
+      <c r="J29" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="K29" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L29" s="2"/>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>1936</v>
       </c>
@@ -39759,15 +40236,16 @@
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-      <c r="I30" s="2" t="s">
+      <c r="I30" s="2"/>
+      <c r="J30" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="K30" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>1843</v>
       </c>
@@ -39784,15 +40262,16 @@
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-      <c r="I31" s="2" t="s">
+      <c r="I31" s="2"/>
+      <c r="J31" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="K31" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>1938</v>
       </c>
@@ -39809,15 +40288,16 @@
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="2" t="s">
+      <c r="I32" s="2"/>
+      <c r="J32" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="K32" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>1940</v>
       </c>
@@ -39834,15 +40314,16 @@
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-      <c r="I33" s="2" t="s">
+      <c r="I33" s="2"/>
+      <c r="J33" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="K33" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L33" s="2"/>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>1941</v>
       </c>
@@ -39863,15 +40344,16 @@
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="2" t="s">
+      <c r="I34" s="2"/>
+      <c r="J34" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="K34" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>1512</v>
       </c>
@@ -39888,15 +40370,18 @@
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-      <c r="I35" s="2" t="s">
+      <c r="I35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="K35" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>1414</v>
       </c>
@@ -39913,15 +40398,16 @@
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-      <c r="I36" s="2" t="s">
+      <c r="I36" s="2"/>
+      <c r="J36" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="K36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>1943</v>
       </c>
@@ -39938,15 +40424,16 @@
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="2" t="s">
+      <c r="I37" s="2"/>
+      <c r="J37" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="K37" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L37" s="2"/>
+    </row>
+    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>1944</v>
       </c>
@@ -39963,15 +40450,16 @@
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="2" t="s">
+      <c r="I38" s="2"/>
+      <c r="J38" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="K38" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>1945</v>
       </c>
@@ -39994,15 +40482,16 @@
         <v>1</v>
       </c>
       <c r="H39" s="2"/>
-      <c r="I39" s="2" t="s">
+      <c r="I39" s="2"/>
+      <c r="J39" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J39" s="2" t="s">
+      <c r="K39" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L39" s="2"/>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>1705</v>
       </c>
@@ -40023,15 +40512,16 @@
       <c r="H40" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I40" s="2" t="s">
+      <c r="I40" s="2"/>
+      <c r="J40" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J40" s="2" t="s">
+      <c r="K40" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="K40" s="2"/>
-    </row>
-    <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>1489</v>
       </c>
@@ -40050,15 +40540,16 @@
       <c r="H41" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I41" s="2" t="s">
+      <c r="I41" s="2"/>
+      <c r="J41" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="K41" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>1574</v>
       </c>
@@ -40075,15 +40566,16 @@
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
-      <c r="I42" s="2" t="s">
+      <c r="I42" s="2"/>
+      <c r="J42" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J42" s="2" t="s">
+      <c r="K42" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>1946</v>
       </c>
@@ -40102,15 +40594,16 @@
         <v>1</v>
       </c>
       <c r="H43" s="2"/>
-      <c r="I43" s="2" t="s">
+      <c r="I43" s="2"/>
+      <c r="J43" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J43" s="2" t="s">
+      <c r="K43" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="K43" s="2"/>
-    </row>
-    <row r="44" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L43" s="2"/>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>1947</v>
       </c>
@@ -40127,15 +40620,16 @@
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
-      <c r="I44" s="2" t="s">
+      <c r="I44" s="2"/>
+      <c r="J44" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J44" s="2" t="s">
+      <c r="K44" s="2" t="s">
         <v>1933</v>
       </c>
-      <c r="K44" s="2"/>
-    </row>
-    <row r="45" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L44" s="2"/>
+    </row>
+    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>1948</v>
       </c>
@@ -40158,15 +40652,16 @@
       <c r="H45" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="I45" s="2"/>
+      <c r="J45" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J45" s="2" t="s">
+      <c r="K45" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K45" s="2"/>
-    </row>
-    <row r="46" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L45" s="2"/>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>1950</v>
       </c>
@@ -40183,15 +40678,16 @@
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-      <c r="I46" s="2" t="s">
+      <c r="I46" s="2"/>
+      <c r="J46" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J46" s="2" t="s">
+      <c r="K46" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K46" s="2"/>
-    </row>
-    <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L46" s="2"/>
+    </row>
+    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>1951</v>
       </c>
@@ -40210,15 +40706,16 @@
         <v>1</v>
       </c>
       <c r="H47" s="2"/>
-      <c r="I47" s="2" t="s">
+      <c r="I47" s="2"/>
+      <c r="J47" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J47" s="2" t="s">
+      <c r="K47" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K47" s="2"/>
-    </row>
-    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L47" s="2"/>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>1952</v>
       </c>
@@ -40239,15 +40736,16 @@
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
-      <c r="I48" s="2" t="s">
+      <c r="I48" s="2"/>
+      <c r="J48" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J48" s="2" t="s">
+      <c r="K48" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L48" s="2"/>
+    </row>
+    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>1953</v>
       </c>
@@ -40268,15 +40766,16 @@
       <c r="H49" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I49" s="2" t="s">
+      <c r="I49" s="2"/>
+      <c r="J49" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="K49" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K49" s="2"/>
-    </row>
-    <row r="50" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>1954</v>
       </c>
@@ -40293,15 +40792,16 @@
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
-      <c r="I50" s="2" t="s">
+      <c r="I50" s="2"/>
+      <c r="J50" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J50" s="2" t="s">
+      <c r="K50" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L50" s="2"/>
+    </row>
+    <row r="51" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>1955</v>
       </c>
@@ -40320,15 +40820,16 @@
       <c r="H51" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="I51" s="2"/>
+      <c r="J51" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="K51" s="2" t="s">
         <v>1933</v>
       </c>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L51" s="2"/>
+    </row>
+    <row r="52" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>1956</v>
       </c>
@@ -40347,15 +40848,16 @@
       <c r="H52" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I52" s="2" t="s">
+      <c r="I52" s="2"/>
+      <c r="J52" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J52" s="2" t="s">
+      <c r="K52" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>1957</v>
       </c>
@@ -40376,15 +40878,16 @@
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
-      <c r="I53" s="2" t="s">
+      <c r="I53" s="2"/>
+      <c r="J53" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J53" s="2" t="s">
+      <c r="K53" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L53" s="2"/>
+    </row>
+    <row r="54" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>1958</v>
       </c>
@@ -40401,15 +40904,16 @@
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
-      <c r="I54" s="2" t="s">
+      <c r="I54" s="2"/>
+      <c r="J54" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J54" s="2" t="s">
+      <c r="K54" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K54" s="2"/>
-    </row>
-    <row r="55" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L54" s="2"/>
+    </row>
+    <row r="55" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>1959</v>
       </c>
@@ -40434,15 +40938,16 @@
       <c r="H55" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I55" s="2" t="s">
+      <c r="I55" s="2"/>
+      <c r="J55" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J55" s="2" t="s">
+      <c r="K55" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K55" s="2"/>
-    </row>
-    <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L55" s="2"/>
+    </row>
+    <row r="56" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>1617</v>
       </c>
@@ -40461,15 +40966,16 @@
       <c r="H56" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I56" s="2" t="s">
+      <c r="I56" s="2"/>
+      <c r="J56" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J56" s="2" t="s">
+      <c r="K56" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L56" s="2"/>
+    </row>
+    <row r="57" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>1960</v>
       </c>
@@ -40488,15 +40994,16 @@
         <v>1</v>
       </c>
       <c r="H57" s="2"/>
-      <c r="I57" s="2" t="s">
+      <c r="I57" s="2"/>
+      <c r="J57" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J57" s="2" t="s">
+      <c r="K57" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K57" s="2"/>
-    </row>
-    <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L57" s="2"/>
+    </row>
+    <row r="58" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>1550</v>
       </c>
@@ -40517,15 +41024,16 @@
       <c r="H58" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I58" s="2" t="s">
+      <c r="I58" s="2"/>
+      <c r="J58" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J58" s="2" t="s">
+      <c r="K58" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L58" s="2"/>
+    </row>
+    <row r="59" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>1961</v>
       </c>
@@ -40544,15 +41052,16 @@
       <c r="H59" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I59" s="2" t="s">
+      <c r="I59" s="2"/>
+      <c r="J59" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J59" s="2" t="s">
+      <c r="K59" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L59" s="2"/>
+    </row>
+    <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>1563</v>
       </c>
@@ -40569,15 +41078,18 @@
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
-      <c r="I60" s="2" t="s">
+      <c r="I60" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J60" s="2" t="s">
+      <c r="K60" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L60" s="2"/>
+    </row>
+    <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>1963</v>
       </c>
@@ -40596,15 +41108,16 @@
       <c r="H61" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I61" s="2" t="s">
+      <c r="I61" s="2"/>
+      <c r="J61" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J61" s="2" t="s">
+      <c r="K61" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K61" s="2"/>
-    </row>
-    <row r="62" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L61" s="2"/>
+    </row>
+    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>1964</v>
       </c>
@@ -40623,15 +41136,16 @@
       <c r="H62" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I62" s="2" t="s">
+      <c r="I62" s="2"/>
+      <c r="J62" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J62" s="2" t="s">
+      <c r="K62" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="2"/>
-    </row>
-    <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L62" s="2"/>
+    </row>
+    <row r="63" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>1965</v>
       </c>
@@ -40652,17 +41166,18 @@
       <c r="H63" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I63" s="2" t="s">
+      <c r="I63" s="2"/>
+      <c r="J63" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J63" s="2" t="s">
+      <c r="K63" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="K63" s="2" t="s">
+      <c r="L63" s="2" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>1312</v>
       </c>
@@ -40679,15 +41194,16 @@
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
-      <c r="I64" s="2" t="s">
+      <c r="I64" s="2"/>
+      <c r="J64" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J64" s="2" t="s">
+      <c r="K64" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K64" s="2"/>
-    </row>
-    <row r="65" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L64" s="2"/>
+    </row>
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>1966</v>
       </c>
@@ -40708,15 +41224,16 @@
       <c r="H65" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I65" s="2" t="s">
+      <c r="I65" s="2"/>
+      <c r="J65" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J65" s="2" t="s">
+      <c r="K65" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K65" s="2"/>
-    </row>
-    <row r="66" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L65" s="2"/>
+    </row>
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>1967</v>
       </c>
@@ -40733,15 +41250,16 @@
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
-      <c r="I66" s="2" t="s">
+      <c r="I66" s="2"/>
+      <c r="J66" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J66" s="2" t="s">
+      <c r="K66" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="K66" s="2"/>
-    </row>
-    <row r="67" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L66" s="2"/>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>1778</v>
       </c>
@@ -40762,15 +41280,16 @@
       <c r="H67" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I67" s="2" t="s">
+      <c r="I67" s="2"/>
+      <c r="J67" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J67" s="2" t="s">
+      <c r="K67" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K67" s="2"/>
-    </row>
-    <row r="68" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L67" s="2"/>
+    </row>
+    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>1968</v>
       </c>
@@ -40787,15 +41306,16 @@
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
-      <c r="I68" s="2" t="s">
+      <c r="I68" s="2"/>
+      <c r="J68" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J68" s="2" t="s">
+      <c r="K68" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="K68" s="2"/>
-    </row>
-    <row r="69" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L68" s="2"/>
+    </row>
+    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>1969</v>
       </c>
@@ -40816,15 +41336,16 @@
       <c r="H69" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I69" s="2" t="s">
+      <c r="I69" s="2"/>
+      <c r="J69" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J69" s="2" t="s">
+      <c r="K69" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K69" s="2"/>
-    </row>
-    <row r="70" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L69" s="2"/>
+    </row>
+    <row r="70" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>1970</v>
       </c>
@@ -40841,15 +41362,16 @@
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
-      <c r="I70" s="2" t="s">
+      <c r="I70" s="2"/>
+      <c r="J70" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J70" s="2" t="s">
+      <c r="K70" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="K70" s="2"/>
-    </row>
-    <row r="71" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L70" s="2"/>
+    </row>
+    <row r="71" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>1381</v>
       </c>
@@ -40866,15 +41388,16 @@
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
-      <c r="I71" s="2" t="s">
+      <c r="I71" s="2"/>
+      <c r="J71" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J71" s="2" t="s">
+      <c r="K71" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K71" s="2"/>
-    </row>
-    <row r="72" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L71" s="2"/>
+    </row>
+    <row r="72" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>1385</v>
       </c>
@@ -40895,15 +41418,16 @@
       <c r="H72" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I72" s="2" t="s">
+      <c r="I72" s="2"/>
+      <c r="J72" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J72" s="2" t="s">
+      <c r="K72" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K72" s="2"/>
-    </row>
-    <row r="73" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L72" s="2"/>
+    </row>
+    <row r="73" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>1971</v>
       </c>
@@ -40920,15 +41444,16 @@
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
-      <c r="I73" s="2" t="s">
+      <c r="I73" s="2"/>
+      <c r="J73" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J73" s="2" t="s">
+      <c r="K73" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="K73" s="2"/>
-    </row>
-    <row r="74" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L73" s="2"/>
+    </row>
+    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>1972</v>
       </c>
@@ -40945,15 +41470,16 @@
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
-      <c r="I74" s="2" t="s">
+      <c r="I74" s="2"/>
+      <c r="J74" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J74" s="2" t="s">
+      <c r="K74" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="K74" s="2"/>
-    </row>
-    <row r="75" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L74" s="2"/>
+    </row>
+    <row r="75" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>1973</v>
       </c>
@@ -40970,15 +41496,16 @@
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
-      <c r="I75" s="2" t="s">
+      <c r="I75" s="2"/>
+      <c r="J75" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J75" s="2" t="s">
+      <c r="K75" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="K75" s="2"/>
-    </row>
-    <row r="76" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L75" s="2"/>
+    </row>
+    <row r="76" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>1324</v>
       </c>
@@ -40995,15 +41522,16 @@
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
-      <c r="I76" s="2" t="s">
+      <c r="I76" s="2"/>
+      <c r="J76" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J76" s="2" t="s">
+      <c r="K76" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K76" s="2"/>
-    </row>
-    <row r="77" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L76" s="2"/>
+    </row>
+    <row r="77" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>1974</v>
       </c>
@@ -41024,15 +41552,16 @@
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
-      <c r="I77" s="2" t="s">
+      <c r="I77" s="2"/>
+      <c r="J77" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J77" s="2" t="s">
+      <c r="K77" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K77" s="2"/>
-    </row>
-    <row r="78" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L77" s="2"/>
+    </row>
+    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>1975</v>
       </c>
@@ -41049,15 +41578,18 @@
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
-      <c r="I78" s="2" t="s">
+      <c r="I78" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J78" s="2" t="s">
+      <c r="K78" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K78" s="2"/>
-    </row>
-    <row r="79" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L78" s="2"/>
+    </row>
+    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>1320</v>
       </c>
@@ -41074,15 +41606,16 @@
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
-      <c r="I79" s="2" t="s">
+      <c r="I79" s="2"/>
+      <c r="J79" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J79" s="2" t="s">
+      <c r="K79" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K79" s="2"/>
-    </row>
-    <row r="80" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L79" s="2"/>
+    </row>
+    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>1533</v>
       </c>
@@ -41099,15 +41632,16 @@
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
-      <c r="I80" s="2" t="s">
+      <c r="I80" s="2"/>
+      <c r="J80" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J80" s="2" t="s">
+      <c r="K80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>1694</v>
       </c>
@@ -41124,15 +41658,16 @@
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
-      <c r="I81" s="2" t="s">
+      <c r="I81" s="2"/>
+      <c r="J81" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J81" s="2" t="s">
+      <c r="K81" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K81" s="2"/>
-    </row>
-    <row r="82" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L81" s="2"/>
+    </row>
+    <row r="82" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>1387</v>
       </c>
@@ -41149,15 +41684,16 @@
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
-      <c r="I82" s="2" t="s">
+      <c r="I82" s="2"/>
+      <c r="J82" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J82" s="2" t="s">
+      <c r="K82" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K82" s="2"/>
-    </row>
-    <row r="83" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L82" s="2"/>
+    </row>
+    <row r="83" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>1976</v>
       </c>
@@ -41174,15 +41710,18 @@
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
-      <c r="I83" s="2" t="s">
+      <c r="I83" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J83" s="2" t="s">
+      <c r="K83" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K83" s="2"/>
-    </row>
-    <row r="84" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L83" s="2"/>
+    </row>
+    <row r="84" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>1626</v>
       </c>
@@ -41199,15 +41738,16 @@
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
-      <c r="I84" s="2" t="s">
+      <c r="I84" s="2"/>
+      <c r="J84" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J84" s="2" t="s">
+      <c r="K84" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K84" s="2"/>
-    </row>
-    <row r="85" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L84" s="2"/>
+    </row>
+    <row r="85" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>1977</v>
       </c>
@@ -41228,15 +41768,16 @@
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
-      <c r="I85" s="2" t="s">
+      <c r="I85" s="2"/>
+      <c r="J85" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J85" s="2" t="s">
+      <c r="K85" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K85" s="2"/>
-    </row>
-    <row r="86" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L85" s="2"/>
+    </row>
+    <row r="86" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>1373</v>
       </c>
@@ -41253,15 +41794,16 @@
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
-      <c r="I86" s="2" t="s">
+      <c r="I86" s="2"/>
+      <c r="J86" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J86" s="2" t="s">
+      <c r="K86" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K86" s="2"/>
-    </row>
-    <row r="87" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L86" s="2"/>
+    </row>
+    <row r="87" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>1978</v>
       </c>
@@ -41282,15 +41824,16 @@
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
-      <c r="I87" s="2" t="s">
+      <c r="I87" s="2"/>
+      <c r="J87" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J87" s="2" t="s">
+      <c r="K87" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K87" s="2"/>
-    </row>
-    <row r="88" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L87" s="2"/>
+    </row>
+    <row r="88" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>1979</v>
       </c>
@@ -41311,15 +41854,16 @@
       <c r="H88" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I88" s="2" t="s">
+      <c r="I88" s="2"/>
+      <c r="J88" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J88" s="2" t="s">
+      <c r="K88" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K88" s="2"/>
-    </row>
-    <row r="89" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L88" s="2"/>
+    </row>
+    <row r="89" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>1580</v>
       </c>
@@ -41338,15 +41882,16 @@
         <v>1</v>
       </c>
       <c r="H89" s="2"/>
-      <c r="I89" s="2" t="s">
+      <c r="I89" s="2"/>
+      <c r="J89" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J89" s="2" t="s">
+      <c r="K89" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K89" s="2"/>
-    </row>
-    <row r="90" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L89" s="2"/>
+    </row>
+    <row r="90" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>1980</v>
       </c>
@@ -41363,15 +41908,16 @@
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
-      <c r="I90" s="2" t="s">
+      <c r="I90" s="2"/>
+      <c r="J90" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J90" s="2" t="s">
+      <c r="K90" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K90" s="2"/>
-    </row>
-    <row r="91" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L90" s="2"/>
+    </row>
+    <row r="91" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>1981</v>
       </c>
@@ -41388,15 +41934,16 @@
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
-      <c r="I91" s="2" t="s">
+      <c r="I91" s="2"/>
+      <c r="J91" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J91" s="2" t="s">
+      <c r="K91" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K91" s="2"/>
-    </row>
-    <row r="92" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L91" s="2"/>
+    </row>
+    <row r="92" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>1863</v>
       </c>
@@ -41413,15 +41960,16 @@
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
-      <c r="I92" s="2" t="s">
+      <c r="I92" s="2"/>
+      <c r="J92" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J92" s="2" t="s">
+      <c r="K92" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K92" s="2"/>
-    </row>
-    <row r="93" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L92" s="2"/>
+    </row>
+    <row r="93" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>1982</v>
       </c>
@@ -41440,15 +41988,16 @@
         <v>1</v>
       </c>
       <c r="H93" s="2"/>
-      <c r="I93" s="2" t="s">
+      <c r="I93" s="2"/>
+      <c r="J93" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J93" s="2" t="s">
+      <c r="K93" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K93" s="2"/>
-    </row>
-    <row r="94" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L93" s="2"/>
+    </row>
+    <row r="94" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>1857</v>
       </c>
@@ -41465,15 +42014,18 @@
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
-      <c r="I94" s="2" t="s">
+      <c r="I94" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J94" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J94" s="2" t="s">
+      <c r="K94" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="2"/>
-    </row>
-    <row r="95" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L94" s="2"/>
+    </row>
+    <row r="95" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>1443</v>
       </c>
@@ -41490,15 +42042,18 @@
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
-      <c r="I95" s="2" t="s">
+      <c r="I95" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J95" s="2" t="s">
+      <c r="K95" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K95" s="2"/>
-    </row>
-    <row r="96" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L95" s="2"/>
+    </row>
+    <row r="96" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>1392</v>
       </c>
@@ -41515,15 +42070,16 @@
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
-      <c r="I96" s="2" t="s">
+      <c r="I96" s="2"/>
+      <c r="J96" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J96" s="2" t="s">
+      <c r="K96" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K96" s="2"/>
-    </row>
-    <row r="97" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L96" s="2"/>
+    </row>
+    <row r="97" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>1983</v>
       </c>
@@ -41544,15 +42100,16 @@
       <c r="H97" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I97" s="2" t="s">
+      <c r="I97" s="2"/>
+      <c r="J97" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J97" s="2" t="s">
+      <c r="K97" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K97" s="2"/>
-    </row>
-    <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L97" s="2"/>
+    </row>
+    <row r="98" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>1519</v>
       </c>
@@ -41573,15 +42130,16 @@
       <c r="H98" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I98" s="2" t="s">
+      <c r="I98" s="2"/>
+      <c r="J98" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J98" s="2" t="s">
+      <c r="K98" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K98" s="2"/>
-    </row>
-    <row r="99" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L98" s="2"/>
+    </row>
+    <row r="99" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>1652</v>
       </c>
@@ -41598,15 +42156,16 @@
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
-      <c r="I99" s="2" t="s">
+      <c r="I99" s="2"/>
+      <c r="J99" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J99" s="2" t="s">
+      <c r="K99" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K99" s="2"/>
-    </row>
-    <row r="100" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L99" s="2"/>
+    </row>
+    <row r="100" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>1358</v>
       </c>
@@ -41623,15 +42182,16 @@
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
-      <c r="I100" s="2" t="s">
+      <c r="I100" s="2"/>
+      <c r="J100" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J100" s="2" t="s">
+      <c r="K100" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K100" s="2"/>
-    </row>
-    <row r="101" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L100" s="2"/>
+    </row>
+    <row r="101" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>1984</v>
       </c>
@@ -41652,15 +42212,16 @@
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
-      <c r="I101" s="2" t="s">
+      <c r="I101" s="2"/>
+      <c r="J101" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J101" s="2" t="s">
+      <c r="K101" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K101" s="2"/>
-    </row>
-    <row r="102" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L101" s="2"/>
+    </row>
+    <row r="102" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>1985</v>
       </c>
@@ -41677,15 +42238,16 @@
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
-      <c r="I102" s="2" t="s">
+      <c r="I102" s="2"/>
+      <c r="J102" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J102" s="2" t="s">
+      <c r="K102" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K102" s="2"/>
-    </row>
-    <row r="103" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L102" s="2"/>
+    </row>
+    <row r="103" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>1389</v>
       </c>
@@ -41704,15 +42266,16 @@
         <v>1</v>
       </c>
       <c r="H103" s="2"/>
-      <c r="I103" s="2" t="s">
+      <c r="I103" s="2"/>
+      <c r="J103" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J103" s="2" t="s">
+      <c r="K103" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K103" s="2"/>
-    </row>
-    <row r="104" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L103" s="2"/>
+    </row>
+    <row r="104" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>1448</v>
       </c>
@@ -41731,15 +42294,16 @@
         <v>1</v>
       </c>
       <c r="H104" s="2"/>
-      <c r="I104" s="2" t="s">
+      <c r="I104" s="2"/>
+      <c r="J104" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J104" s="2" t="s">
+      <c r="K104" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K104" s="2"/>
-    </row>
-    <row r="105" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L104" s="2"/>
+    </row>
+    <row r="105" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>1986</v>
       </c>
@@ -41760,15 +42324,16 @@
       <c r="H105" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I105" s="2" t="s">
+      <c r="I105" s="2"/>
+      <c r="J105" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J105" s="2" t="s">
+      <c r="K105" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="K105" s="2"/>
-    </row>
-    <row r="106" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L105" s="2"/>
+    </row>
+    <row r="106" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>1987</v>
       </c>
@@ -41789,15 +42354,16 @@
       <c r="H106" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I106" s="2" t="s">
+      <c r="I106" s="2"/>
+      <c r="J106" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J106" s="2" t="s">
+      <c r="K106" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K106" s="2"/>
-    </row>
-    <row r="107" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L106" s="2"/>
+    </row>
+    <row r="107" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>1988</v>
       </c>
@@ -41814,15 +42380,16 @@
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
-      <c r="I107" s="2" t="s">
+      <c r="I107" s="2"/>
+      <c r="J107" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J107" s="2" t="s">
+      <c r="K107" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K107" s="2"/>
-    </row>
-    <row r="108" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L107" s="2"/>
+    </row>
+    <row r="108" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>1309</v>
       </c>
@@ -41839,15 +42406,16 @@
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
-      <c r="I108" s="2" t="s">
+      <c r="I108" s="2"/>
+      <c r="J108" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J108" s="2" t="s">
+      <c r="K108" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K108" s="2"/>
-    </row>
-    <row r="109" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L108" s="2"/>
+    </row>
+    <row r="109" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>1989</v>
       </c>
@@ -41870,15 +42438,16 @@
       <c r="H109" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I109" s="2" t="s">
+      <c r="I109" s="2"/>
+      <c r="J109" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J109" s="2" t="s">
+      <c r="K109" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K109" s="2"/>
-    </row>
-    <row r="110" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L109" s="2"/>
+    </row>
+    <row r="110" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>1556</v>
       </c>
@@ -41895,15 +42464,16 @@
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
-      <c r="I110" s="2" t="s">
+      <c r="I110" s="2"/>
+      <c r="J110" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J110" s="2" t="s">
+      <c r="K110" s="2" t="s">
         <v>1990</v>
       </c>
-      <c r="K110" s="2"/>
-    </row>
-    <row r="111" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L110" s="2"/>
+    </row>
+    <row r="111" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>1590</v>
       </c>
@@ -41920,15 +42490,16 @@
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
-      <c r="I111" s="2" t="s">
+      <c r="I111" s="2"/>
+      <c r="J111" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J111" s="2" t="s">
+      <c r="K111" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="K111" s="2"/>
-    </row>
-    <row r="112" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L111" s="2"/>
+    </row>
+    <row r="112" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>1400</v>
       </c>
@@ -41949,15 +42520,16 @@
       <c r="H112" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I112" s="2" t="s">
+      <c r="I112" s="2"/>
+      <c r="J112" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J112" s="2" t="s">
+      <c r="K112" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K112" s="2"/>
-    </row>
-    <row r="113" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L112" s="2"/>
+    </row>
+    <row r="113" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>1683</v>
       </c>
@@ -41974,15 +42546,16 @@
       </c>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
-      <c r="I113" s="2" t="s">
+      <c r="I113" s="2"/>
+      <c r="J113" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J113" s="2" t="s">
+      <c r="K113" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K113" s="2"/>
-    </row>
-    <row r="114" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L113" s="2"/>
+    </row>
+    <row r="114" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>1576</v>
       </c>
@@ -41999,15 +42572,16 @@
       </c>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
-      <c r="I114" s="2" t="s">
+      <c r="I114" s="2"/>
+      <c r="J114" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J114" s="2" t="s">
+      <c r="K114" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K114" s="2"/>
-    </row>
-    <row r="115" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L114" s="2"/>
+    </row>
+    <row r="115" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>1714</v>
       </c>
@@ -42024,15 +42598,16 @@
       </c>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
-      <c r="I115" s="2" t="s">
+      <c r="I115" s="2"/>
+      <c r="J115" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J115" s="2" t="s">
+      <c r="K115" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K115" s="2"/>
-    </row>
-    <row r="116" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L115" s="2"/>
+    </row>
+    <row r="116" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>1991</v>
       </c>
@@ -42053,15 +42628,16 @@
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
-      <c r="I116" s="2" t="s">
+      <c r="I116" s="2"/>
+      <c r="J116" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J116" s="2" t="s">
+      <c r="K116" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K116" s="2"/>
-    </row>
-    <row r="117" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L116" s="2"/>
+    </row>
+    <row r="117" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>1992</v>
       </c>
@@ -42080,17 +42656,18 @@
       <c r="H117" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I117" s="2" t="s">
+      <c r="I117" s="2"/>
+      <c r="J117" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J117" s="2" t="s">
+      <c r="K117" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="K117" s="2" t="s">
+      <c r="L117" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>1655</v>
       </c>
@@ -42107,15 +42684,16 @@
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
-      <c r="I118" s="2" t="s">
+      <c r="I118" s="2"/>
+      <c r="J118" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J118" s="2" t="s">
+      <c r="K118" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K118" s="2"/>
-    </row>
-    <row r="119" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L118" s="2"/>
+    </row>
+    <row r="119" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>1993</v>
       </c>
@@ -42134,15 +42712,16 @@
       <c r="H119" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I119" s="2" t="s">
+      <c r="I119" s="2"/>
+      <c r="J119" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J119" s="2" t="s">
+      <c r="K119" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K119" s="2"/>
-    </row>
-    <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L119" s="2"/>
+    </row>
+    <row r="120" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>1994</v>
       </c>
@@ -42159,15 +42738,16 @@
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
-      <c r="I120" s="2" t="s">
+      <c r="I120" s="2"/>
+      <c r="J120" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J120" s="2" t="s">
+      <c r="K120" s="2" t="s">
         <v>1931</v>
       </c>
-      <c r="K120" s="2"/>
-    </row>
-    <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L120" s="2"/>
+    </row>
+    <row r="121" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>1995</v>
       </c>
@@ -42186,15 +42766,16 @@
         <v>1</v>
       </c>
       <c r="H121" s="2"/>
-      <c r="I121" s="2" t="s">
+      <c r="I121" s="2"/>
+      <c r="J121" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J121" s="2" t="s">
+      <c r="K121" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K121" s="2"/>
-    </row>
-    <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L121" s="2"/>
+    </row>
+    <row r="122" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>1996</v>
       </c>
@@ -42211,15 +42792,18 @@
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
-      <c r="I122" s="2" t="s">
+      <c r="I122" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J122" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J122" s="2" t="s">
+      <c r="K122" s="2" t="s">
         <v>1216</v>
       </c>
-      <c r="K122" s="2"/>
-    </row>
-    <row r="123" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L122" s="2"/>
+    </row>
+    <row r="123" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>1997</v>
       </c>
@@ -42236,15 +42820,18 @@
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
-      <c r="I123" s="2" t="s">
+      <c r="I123" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J123" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J123" s="2" t="s">
+      <c r="K123" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K123" s="2"/>
-    </row>
-    <row r="124" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L123" s="2"/>
+    </row>
+    <row r="124" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>1998</v>
       </c>
@@ -42261,15 +42848,16 @@
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
-      <c r="I124" s="2" t="s">
+      <c r="I124" s="2"/>
+      <c r="J124" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J124" s="2" t="s">
+      <c r="K124" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K124" s="2"/>
-    </row>
-    <row r="125" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L124" s="2"/>
+    </row>
+    <row r="125" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>1361</v>
       </c>
@@ -42286,15 +42874,16 @@
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
-      <c r="I125" s="2" t="s">
+      <c r="I125" s="2"/>
+      <c r="J125" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J125" s="2" t="s">
+      <c r="K125" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K125" s="2"/>
-    </row>
-    <row r="126" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L125" s="2"/>
+    </row>
+    <row r="126" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>1999</v>
       </c>
@@ -42317,15 +42906,16 @@
       <c r="H126" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I126" s="2" t="s">
+      <c r="I126" s="2"/>
+      <c r="J126" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J126" s="2" t="s">
+      <c r="K126" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K126" s="2"/>
-    </row>
-    <row r="127" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L126" s="2"/>
+    </row>
+    <row r="127" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>2000</v>
       </c>
@@ -42346,15 +42936,16 @@
       <c r="H127" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I127" s="2" t="s">
+      <c r="I127" s="2"/>
+      <c r="J127" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J127" s="2" t="s">
+      <c r="K127" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K127" s="2"/>
-    </row>
-    <row r="128" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L127" s="2"/>
+    </row>
+    <row r="128" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>1689</v>
       </c>
@@ -42373,15 +42964,16 @@
         <v>1</v>
       </c>
       <c r="H128" s="2"/>
-      <c r="I128" s="2" t="s">
+      <c r="I128" s="2"/>
+      <c r="J128" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J128" s="2" t="s">
+      <c r="K128" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K128" s="2"/>
-    </row>
-    <row r="129" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L128" s="2"/>
+    </row>
+    <row r="129" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>2001</v>
       </c>
@@ -42400,15 +42992,16 @@
       <c r="H129" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I129" s="2" t="s">
+      <c r="I129" s="2"/>
+      <c r="J129" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J129" s="2" t="s">
+      <c r="K129" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K129" s="2"/>
-    </row>
-    <row r="130" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L129" s="2"/>
+    </row>
+    <row r="130" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>1339</v>
       </c>
@@ -42425,15 +43018,16 @@
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
-      <c r="I130" s="2" t="s">
+      <c r="I130" s="2"/>
+      <c r="J130" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J130" s="2" t="s">
+      <c r="K130" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K130" s="2"/>
-    </row>
-    <row r="131" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L130" s="2"/>
+    </row>
+    <row r="131" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>1296</v>
       </c>
@@ -42452,15 +43046,16 @@
       <c r="H131" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I131" s="2" t="s">
+      <c r="I131" s="2"/>
+      <c r="J131" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J131" s="2" t="s">
+      <c r="K131" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K131" s="2"/>
-    </row>
-    <row r="132" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L131" s="2"/>
+    </row>
+    <row r="132" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>2002</v>
       </c>
@@ -42483,15 +43078,16 @@
       <c r="H132" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I132" s="2" t="s">
+      <c r="I132" s="2"/>
+      <c r="J132" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J132" s="2" t="s">
+      <c r="K132" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K132" s="2"/>
-    </row>
-    <row r="133" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L132" s="2"/>
+    </row>
+    <row r="133" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>2003</v>
       </c>
@@ -42510,15 +43106,16 @@
       <c r="H133" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I133" s="2" t="s">
+      <c r="I133" s="2"/>
+      <c r="J133" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J133" s="2" t="s">
+      <c r="K133" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K133" s="2"/>
-    </row>
-    <row r="134" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L133" s="2"/>
+    </row>
+    <row r="134" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>2004</v>
       </c>
@@ -42539,15 +43136,16 @@
       <c r="H134" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I134" s="2" t="s">
+      <c r="I134" s="2"/>
+      <c r="J134" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J134" s="2" t="s">
+      <c r="K134" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K134" s="2"/>
-    </row>
-    <row r="135" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L134" s="2"/>
+    </row>
+    <row r="135" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>1865</v>
       </c>
@@ -42564,15 +43162,16 @@
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
-      <c r="I135" s="2" t="s">
+      <c r="I135" s="2"/>
+      <c r="J135" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J135" s="2" t="s">
+      <c r="K135" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K135" s="2"/>
-    </row>
-    <row r="136" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L135" s="2"/>
+    </row>
+    <row r="136" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>1832</v>
       </c>
@@ -42591,15 +43190,16 @@
         <v>1</v>
       </c>
       <c r="H136" s="2"/>
-      <c r="I136" s="2" t="s">
+      <c r="I136" s="2"/>
+      <c r="J136" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J136" s="2" t="s">
+      <c r="K136" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K136" s="2"/>
-    </row>
-    <row r="137" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L136" s="2"/>
+    </row>
+    <row r="137" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>1322</v>
       </c>
@@ -42616,15 +43216,16 @@
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
-      <c r="I137" s="2" t="s">
+      <c r="I137" s="2"/>
+      <c r="J137" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J137" s="2" t="s">
+      <c r="K137" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K137" s="2"/>
-    </row>
-    <row r="138" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L137" s="2"/>
+    </row>
+    <row r="138" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>2005</v>
       </c>
@@ -42641,15 +43242,16 @@
       </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
-      <c r="I138" s="2" t="s">
+      <c r="I138" s="2"/>
+      <c r="J138" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J138" s="2" t="s">
+      <c r="K138" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K138" s="2"/>
-    </row>
-    <row r="139" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L138" s="2"/>
+    </row>
+    <row r="139" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>2006</v>
       </c>
@@ -42668,17 +43270,18 @@
       <c r="H139" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I139" s="2" t="s">
+      <c r="I139" s="2"/>
+      <c r="J139" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J139" s="2" t="s">
+      <c r="K139" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="K139" s="2" t="s">
+      <c r="L139" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>2007</v>
       </c>
@@ -42699,15 +43302,16 @@
       <c r="H140" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I140" s="2" t="s">
+      <c r="I140" s="2"/>
+      <c r="J140" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J140" s="2" t="s">
+      <c r="K140" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="K140" s="2"/>
-    </row>
-    <row r="141" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L140" s="2"/>
+    </row>
+    <row r="141" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>1328</v>
       </c>
@@ -42724,15 +43328,16 @@
       </c>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
-      <c r="I141" s="2" t="s">
+      <c r="I141" s="2"/>
+      <c r="J141" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J141" s="2" t="s">
+      <c r="K141" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K141" s="2"/>
-    </row>
-    <row r="142" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L141" s="2"/>
+    </row>
+    <row r="142" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>2008</v>
       </c>
@@ -42753,17 +43358,18 @@
       <c r="H142" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I142" s="2" t="s">
+      <c r="I142" s="2"/>
+      <c r="J142" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J142" s="2" t="s">
+      <c r="K142" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="K142" s="2" t="s">
+      <c r="L142" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>2009</v>
       </c>
@@ -42780,15 +43386,16 @@
       </c>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
-      <c r="I143" s="2" t="s">
+      <c r="I143" s="2"/>
+      <c r="J143" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J143" s="2" t="s">
+      <c r="K143" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K143" s="2"/>
-    </row>
-    <row r="144" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L143" s="2"/>
+    </row>
+    <row r="144" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>1558</v>
       </c>
@@ -42805,15 +43412,16 @@
       </c>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
-      <c r="I144" s="2" t="s">
+      <c r="I144" s="2"/>
+      <c r="J144" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J144" s="2" t="s">
+      <c r="K144" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K144" s="2"/>
-    </row>
-    <row r="145" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L144" s="2"/>
+    </row>
+    <row r="145" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>1611</v>
       </c>
@@ -42830,15 +43438,16 @@
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
-      <c r="I145" s="2" t="s">
+      <c r="I145" s="2"/>
+      <c r="J145" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J145" s="2" t="s">
+      <c r="K145" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K145" s="2"/>
-    </row>
-    <row r="146" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L145" s="2"/>
+    </row>
+    <row r="146" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>1316</v>
       </c>
@@ -42859,15 +43468,16 @@
       <c r="H146" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I146" s="2" t="s">
+      <c r="I146" s="2"/>
+      <c r="J146" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J146" s="2" t="s">
+      <c r="K146" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K146" s="2"/>
-    </row>
-    <row r="147" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L146" s="2"/>
+    </row>
+    <row r="147" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>2010</v>
       </c>
@@ -42884,15 +43494,16 @@
       </c>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
-      <c r="I147" s="2" t="s">
+      <c r="I147" s="2"/>
+      <c r="J147" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J147" s="2" t="s">
+      <c r="K147" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K147" s="2"/>
-    </row>
-    <row r="148" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L147" s="2"/>
+    </row>
+    <row r="148" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>1330</v>
       </c>
@@ -42911,15 +43522,16 @@
       <c r="H148" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I148" s="2" t="s">
+      <c r="I148" s="2"/>
+      <c r="J148" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J148" s="2" t="s">
+      <c r="K148" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K148" s="2"/>
-    </row>
-    <row r="149" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L148" s="2"/>
+    </row>
+    <row r="149" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>1303</v>
       </c>
@@ -42940,15 +43552,16 @@
       <c r="H149" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I149" s="2" t="s">
+      <c r="I149" s="2"/>
+      <c r="J149" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J149" s="2" t="s">
+      <c r="K149" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K149" s="2"/>
-    </row>
-    <row r="150" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L149" s="2"/>
+    </row>
+    <row r="150" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>1728</v>
       </c>
@@ -42969,15 +43582,16 @@
       <c r="H150" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I150" s="2" t="s">
+      <c r="I150" s="2"/>
+      <c r="J150" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J150" s="2" t="s">
+      <c r="K150" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K150" s="2"/>
-    </row>
-    <row r="151" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L150" s="2"/>
+    </row>
+    <row r="151" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>2011</v>
       </c>
@@ -42994,15 +43608,18 @@
       </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
-      <c r="I151" s="2" t="s">
+      <c r="I151" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J151" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J151" s="2" t="s">
+      <c r="K151" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K151" s="2"/>
-    </row>
-    <row r="152" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L151" s="2"/>
+    </row>
+    <row r="152" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>1664</v>
       </c>
@@ -43023,15 +43640,16 @@
       <c r="H152" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I152" s="2" t="s">
+      <c r="I152" s="2"/>
+      <c r="J152" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J152" s="2" t="s">
+      <c r="K152" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K152" s="2"/>
-    </row>
-    <row r="153" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L152" s="2"/>
+    </row>
+    <row r="153" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>1889</v>
       </c>
@@ -43048,15 +43666,16 @@
       </c>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
-      <c r="I153" s="2" t="s">
+      <c r="I153" s="2"/>
+      <c r="J153" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J153" s="2" t="s">
+      <c r="K153" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K153" s="2"/>
-    </row>
-    <row r="154" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L153" s="2"/>
+    </row>
+    <row r="154" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>2012</v>
       </c>
@@ -43077,15 +43696,16 @@
       <c r="H154" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I154" s="2" t="s">
+      <c r="I154" s="2"/>
+      <c r="J154" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J154" s="2" t="s">
+      <c r="K154" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K154" s="2"/>
-    </row>
-    <row r="155" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L154" s="2"/>
+    </row>
+    <row r="155" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>2013</v>
       </c>
@@ -43102,15 +43722,16 @@
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
-      <c r="I155" s="2" t="s">
+      <c r="I155" s="2"/>
+      <c r="J155" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J155" s="2" t="s">
+      <c r="K155" s="2" t="s">
         <v>1931</v>
       </c>
-      <c r="K155" s="2"/>
-    </row>
-    <row r="156" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L155" s="2"/>
+    </row>
+    <row r="156" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>2014</v>
       </c>
@@ -43129,15 +43750,16 @@
       <c r="H156" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I156" s="2" t="s">
+      <c r="I156" s="2"/>
+      <c r="J156" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J156" s="2" t="s">
+      <c r="K156" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K156" s="2"/>
-    </row>
-    <row r="157" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L156" s="2"/>
+    </row>
+    <row r="157" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>2015</v>
       </c>
@@ -43158,15 +43780,16 @@
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
-      <c r="I157" s="2" t="s">
+      <c r="I157" s="2"/>
+      <c r="J157" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J157" s="2" t="s">
+      <c r="K157" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K157" s="2"/>
-    </row>
-    <row r="158" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L157" s="2"/>
+    </row>
+    <row r="158" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>2016</v>
       </c>
@@ -43187,15 +43810,16 @@
       <c r="H158" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I158" s="2" t="s">
+      <c r="I158" s="2"/>
+      <c r="J158" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J158" s="2" t="s">
+      <c r="K158" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K158" s="2"/>
-    </row>
-    <row r="159" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L158" s="2"/>
+    </row>
+    <row r="159" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>1307</v>
       </c>
@@ -43212,15 +43836,16 @@
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
-      <c r="I159" s="2" t="s">
+      <c r="I159" s="2"/>
+      <c r="J159" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J159" s="2" t="s">
+      <c r="K159" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K159" s="2"/>
-    </row>
-    <row r="160" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L159" s="2"/>
+    </row>
+    <row r="160" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>2017</v>
       </c>
@@ -43243,15 +43868,16 @@
       <c r="H160" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I160" s="2" t="s">
+      <c r="I160" s="2"/>
+      <c r="J160" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J160" s="2" t="s">
+      <c r="K160" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K160" s="2"/>
-    </row>
-    <row r="161" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L160" s="2"/>
+    </row>
+    <row r="161" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>2018</v>
       </c>
@@ -43270,15 +43896,16 @@
       <c r="H161" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I161" s="2" t="s">
+      <c r="I161" s="2"/>
+      <c r="J161" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J161" s="2" t="s">
+      <c r="K161" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K161" s="2"/>
-    </row>
-    <row r="162" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L161" s="2"/>
+    </row>
+    <row r="162" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>1872</v>
       </c>
@@ -43295,15 +43922,16 @@
       </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
-      <c r="I162" s="2" t="s">
+      <c r="I162" s="2"/>
+      <c r="J162" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J162" s="2" t="s">
+      <c r="K162" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K162" s="2"/>
-    </row>
-    <row r="163" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L162" s="2"/>
+    </row>
+    <row r="163" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>2019</v>
       </c>
@@ -43324,15 +43952,16 @@
       <c r="H163" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I163" s="2" t="s">
+      <c r="I163" s="2"/>
+      <c r="J163" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J163" s="2" t="s">
+      <c r="K163" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K163" s="2"/>
-    </row>
-    <row r="164" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L163" s="2"/>
+    </row>
+    <row r="164" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>1342</v>
       </c>
@@ -43349,15 +43978,16 @@
       </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
-      <c r="I164" s="2" t="s">
+      <c r="I164" s="2"/>
+      <c r="J164" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J164" s="2" t="s">
+      <c r="K164" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K164" s="2"/>
-    </row>
-    <row r="165" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L164" s="2"/>
+    </row>
+    <row r="165" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>2020</v>
       </c>
@@ -43374,15 +44004,16 @@
       </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
-      <c r="I165" s="2" t="s">
+      <c r="I165" s="2"/>
+      <c r="J165" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J165" s="2" t="s">
+      <c r="K165" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="K165" s="2"/>
-    </row>
-    <row r="166" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L165" s="2"/>
+    </row>
+    <row r="166" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>2021</v>
       </c>
@@ -43399,15 +44030,16 @@
       </c>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
-      <c r="I166" s="2" t="s">
+      <c r="I166" s="2"/>
+      <c r="J166" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J166" s="2" t="s">
+      <c r="K166" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="K166" s="2"/>
-    </row>
-    <row r="167" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L166" s="2"/>
+    </row>
+    <row r="167" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>1424</v>
       </c>
@@ -43428,15 +44060,16 @@
       <c r="H167" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I167" s="2" t="s">
+      <c r="I167" s="2"/>
+      <c r="J167" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J167" s="2" t="s">
+      <c r="K167" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K167" s="2"/>
-    </row>
-    <row r="168" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L167" s="2"/>
+    </row>
+    <row r="168" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>1326</v>
       </c>
@@ -43453,15 +44086,16 @@
       </c>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
-      <c r="I168" s="2" t="s">
+      <c r="I168" s="2"/>
+      <c r="J168" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J168" s="2" t="s">
+      <c r="K168" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K168" s="2"/>
-    </row>
-    <row r="169" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L168" s="2"/>
+    </row>
+    <row r="169" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>1300</v>
       </c>
@@ -43480,15 +44114,16 @@
       <c r="H169" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I169" s="2" t="s">
+      <c r="I169" s="2"/>
+      <c r="J169" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J169" s="2" t="s">
+      <c r="K169" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K169" s="2"/>
-    </row>
-    <row r="170" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L169" s="2"/>
+    </row>
+    <row r="170" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>2022</v>
       </c>
@@ -43509,15 +44144,16 @@
       <c r="H170" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I170" s="2" t="s">
+      <c r="I170" s="2"/>
+      <c r="J170" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J170" s="2" t="s">
+      <c r="K170" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K170" s="2"/>
-    </row>
-    <row r="171" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L170" s="2"/>
+    </row>
+    <row r="171" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>2023</v>
       </c>
@@ -43534,15 +44170,18 @@
       </c>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
-      <c r="I171" s="2" t="s">
+      <c r="I171" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J171" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J171" s="2" t="s">
+      <c r="K171" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K171" s="2"/>
-    </row>
-    <row r="172" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L171" s="2"/>
+    </row>
+    <row r="172" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>1697</v>
       </c>
@@ -43563,15 +44202,16 @@
       <c r="H172" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I172" s="2" t="s">
+      <c r="I172" s="2"/>
+      <c r="J172" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J172" s="2" t="s">
+      <c r="K172" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K172" s="2"/>
-    </row>
-    <row r="173" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L172" s="2"/>
+    </row>
+    <row r="173" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>2024</v>
       </c>
@@ -43588,15 +44228,16 @@
       </c>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
-      <c r="I173" s="2" t="s">
+      <c r="I173" s="2"/>
+      <c r="J173" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J173" s="2" t="s">
+      <c r="K173" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K173" s="2"/>
-    </row>
-    <row r="174" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L173" s="2"/>
+    </row>
+    <row r="174" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>2025</v>
       </c>
@@ -43613,15 +44254,16 @@
       </c>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
-      <c r="I174" s="2" t="s">
+      <c r="I174" s="2"/>
+      <c r="J174" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J174" s="2" t="s">
+      <c r="K174" s="2" t="s">
         <v>2027</v>
       </c>
-      <c r="K174" s="2"/>
-    </row>
-    <row r="175" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L174" s="2"/>
+    </row>
+    <row r="175" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>2028</v>
       </c>
@@ -43640,15 +44282,16 @@
       <c r="H175" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I175" s="2" t="s">
+      <c r="I175" s="2"/>
+      <c r="J175" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J175" s="2" t="s">
+      <c r="K175" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="K175" s="2"/>
-    </row>
-    <row r="176" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L175" s="2"/>
+    </row>
+    <row r="176" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>2029</v>
       </c>
@@ -43667,17 +44310,18 @@
       <c r="H176" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I176" s="2" t="s">
+      <c r="I176" s="2"/>
+      <c r="J176" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J176" s="2" t="s">
+      <c r="K176" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="K176" s="2" t="s">
+      <c r="L176" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>2030</v>
       </c>
@@ -43696,17 +44340,20 @@
       <c r="H177" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I177" s="2" t="s">
+      <c r="I177" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J177" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J177" s="2" t="s">
+      <c r="K177" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="K177" s="2" t="s">
+      <c r="L177" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>2031</v>
       </c>
@@ -43723,15 +44370,16 @@
       </c>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
-      <c r="I178" s="2" t="s">
+      <c r="I178" s="2"/>
+      <c r="J178" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J178" s="2" t="s">
+      <c r="K178" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="K178" s="2"/>
-    </row>
-    <row r="179" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L178" s="2"/>
+    </row>
+    <row r="179" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>2032</v>
       </c>
@@ -43748,15 +44396,16 @@
       </c>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
-      <c r="I179" s="2" t="s">
+      <c r="I179" s="2"/>
+      <c r="J179" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J179" s="2" t="s">
+      <c r="K179" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K179" s="2"/>
-    </row>
-    <row r="180" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L179" s="2"/>
+    </row>
+    <row r="180" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>2033</v>
       </c>
@@ -43773,15 +44422,16 @@
       </c>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
-      <c r="I180" s="2" t="s">
+      <c r="I180" s="2"/>
+      <c r="J180" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J180" s="2" t="s">
+      <c r="K180" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K180" s="2"/>
-    </row>
-    <row r="181" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L180" s="2"/>
+    </row>
+    <row r="181" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>2034</v>
       </c>
@@ -43802,15 +44452,16 @@
       <c r="H181" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I181" s="2" t="s">
+      <c r="I181" s="2"/>
+      <c r="J181" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J181" s="2" t="s">
+      <c r="K181" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K181" s="2"/>
-    </row>
-    <row r="182" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L181" s="2"/>
+    </row>
+    <row r="182" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>2035</v>
       </c>
@@ -43827,15 +44478,16 @@
       </c>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
-      <c r="I182" s="2" t="s">
+      <c r="I182" s="2"/>
+      <c r="J182" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J182" s="2" t="s">
+      <c r="K182" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K182" s="2"/>
-    </row>
-    <row r="183" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L182" s="2"/>
+    </row>
+    <row r="183" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>2036</v>
       </c>
@@ -43854,15 +44506,16 @@
       <c r="H183" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I183" s="2" t="s">
+      <c r="I183" s="2"/>
+      <c r="J183" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J183" s="2" t="s">
+      <c r="K183" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K183" s="2"/>
-    </row>
-    <row r="184" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L183" s="2"/>
+    </row>
+    <row r="184" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>2037</v>
       </c>
@@ -43879,15 +44532,16 @@
       </c>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
-      <c r="I184" s="2" t="s">
+      <c r="I184" s="2"/>
+      <c r="J184" s="2" t="s">
         <v>2038</v>
       </c>
-      <c r="J184" s="2" t="s">
+      <c r="K184" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K184" s="2"/>
-    </row>
-    <row r="185" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L184" s="2"/>
+    </row>
+    <row r="185" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>2039</v>
       </c>
@@ -43904,15 +44558,16 @@
       </c>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
-      <c r="I185" s="2" t="s">
+      <c r="I185" s="2"/>
+      <c r="J185" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J185" s="2" t="s">
+      <c r="K185" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K185" s="2"/>
-    </row>
-    <row r="186" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L185" s="2"/>
+    </row>
+    <row r="186" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>2040</v>
       </c>
@@ -43929,15 +44584,16 @@
       </c>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
-      <c r="I186" s="2" t="s">
+      <c r="I186" s="2"/>
+      <c r="J186" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J186" s="2" t="s">
+      <c r="K186" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K186" s="2"/>
-    </row>
-    <row r="187" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L186" s="2"/>
+    </row>
+    <row r="187" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>2041</v>
       </c>
@@ -43954,15 +44610,18 @@
       </c>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
-      <c r="I187" s="2" t="s">
+      <c r="I187" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J187" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J187" s="2" t="s">
+      <c r="K187" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K187" s="2"/>
-    </row>
-    <row r="188" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L187" s="2"/>
+    </row>
+    <row r="188" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>2042</v>
       </c>
@@ -43987,15 +44646,16 @@
       <c r="H188" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I188" s="2" t="s">
+      <c r="I188" s="2"/>
+      <c r="J188" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J188" s="2" t="s">
+      <c r="K188" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K188" s="2"/>
-    </row>
-    <row r="189" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L188" s="2"/>
+    </row>
+    <row r="189" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>1572</v>
       </c>
@@ -44012,15 +44672,16 @@
       </c>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
-      <c r="I189" s="2" t="s">
+      <c r="I189" s="2"/>
+      <c r="J189" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J189" s="2" t="s">
+      <c r="K189" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K189" s="2"/>
-    </row>
-    <row r="190" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L189" s="2"/>
+    </row>
+    <row r="190" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>2043</v>
       </c>
@@ -44041,15 +44702,16 @@
       <c r="H190" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I190" s="2" t="s">
+      <c r="I190" s="2"/>
+      <c r="J190" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J190" s="2" t="s">
+      <c r="K190" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K190" s="2"/>
-    </row>
-    <row r="191" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L190" s="2"/>
+    </row>
+    <row r="191" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>2044</v>
       </c>
@@ -44070,17 +44732,18 @@
       <c r="H191" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I191" s="2" t="s">
+      <c r="I191" s="2"/>
+      <c r="J191" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J191" s="2" t="s">
+      <c r="K191" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="K191" s="2" t="s">
+      <c r="L191" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>2045</v>
       </c>
@@ -44101,15 +44764,16 @@
       <c r="H192" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I192" s="2" t="s">
+      <c r="I192" s="2"/>
+      <c r="J192" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J192" s="2" t="s">
+      <c r="K192" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K192" s="2"/>
-    </row>
-    <row r="193" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L192" s="2"/>
+    </row>
+    <row r="193" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>2046</v>
       </c>
@@ -44126,15 +44790,18 @@
       </c>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
-      <c r="I193" s="2" t="s">
+      <c r="I193" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J193" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J193" s="2" t="s">
+      <c r="K193" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K193" s="2"/>
-    </row>
-    <row r="194" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L193" s="2"/>
+    </row>
+    <row r="194" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>1356</v>
       </c>
@@ -44151,15 +44818,16 @@
       </c>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
-      <c r="I194" s="2" t="s">
+      <c r="I194" s="2"/>
+      <c r="J194" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J194" s="2" t="s">
+      <c r="K194" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K194" s="2"/>
-    </row>
-    <row r="195" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L194" s="2"/>
+    </row>
+    <row r="195" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>2047</v>
       </c>
@@ -44176,15 +44844,16 @@
       </c>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
-      <c r="I195" s="2" t="s">
+      <c r="I195" s="2"/>
+      <c r="J195" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J195" s="2" t="s">
+      <c r="K195" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K195" s="2"/>
-    </row>
-    <row r="196" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L195" s="2"/>
+    </row>
+    <row r="196" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>2048</v>
       </c>
@@ -44201,15 +44870,16 @@
       </c>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
-      <c r="I196" s="2" t="s">
+      <c r="I196" s="2"/>
+      <c r="J196" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J196" s="2" t="s">
+      <c r="K196" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K196" s="2"/>
-    </row>
-    <row r="197" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L196" s="2"/>
+    </row>
+    <row r="197" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>2049</v>
       </c>
@@ -44230,15 +44900,16 @@
       <c r="H197" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I197" s="2" t="s">
+      <c r="I197" s="2"/>
+      <c r="J197" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J197" s="2" t="s">
+      <c r="K197" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K197" s="2"/>
-    </row>
-    <row r="198" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L197" s="2"/>
+    </row>
+    <row r="198" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>2050</v>
       </c>
@@ -44255,15 +44926,16 @@
       </c>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
-      <c r="I198" s="2" t="s">
+      <c r="I198" s="2"/>
+      <c r="J198" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J198" s="2" t="s">
+      <c r="K198" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="K198" s="2"/>
-    </row>
-    <row r="199" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L198" s="2"/>
+    </row>
+    <row r="199" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>2051</v>
       </c>
@@ -44280,15 +44952,16 @@
       </c>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
-      <c r="I199" s="2" t="s">
+      <c r="I199" s="2"/>
+      <c r="J199" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J199" s="2" t="s">
+      <c r="K199" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K199" s="2"/>
-    </row>
-    <row r="200" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L199" s="2"/>
+    </row>
+    <row r="200" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>2052</v>
       </c>
@@ -44305,15 +44978,16 @@
       </c>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
-      <c r="I200" s="2" t="s">
+      <c r="I200" s="2"/>
+      <c r="J200" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J200" s="2" t="s">
+      <c r="K200" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K200" s="2"/>
-    </row>
-    <row r="201" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L200" s="2"/>
+    </row>
+    <row r="201" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>2053</v>
       </c>
@@ -44330,15 +45004,18 @@
       </c>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
-      <c r="I201" s="2" t="s">
+      <c r="I201" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J201" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J201" s="2" t="s">
+      <c r="K201" s="2" t="s">
         <v>1560</v>
       </c>
-      <c r="K201" s="2"/>
-    </row>
-    <row r="202" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L201" s="2"/>
+    </row>
+    <row r="202" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>1672</v>
       </c>
@@ -44359,15 +45036,16 @@
       <c r="H202" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I202" s="2" t="s">
+      <c r="I202" s="2"/>
+      <c r="J202" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J202" s="2" t="s">
+      <c r="K202" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K202" s="2"/>
-    </row>
-    <row r="203" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L202" s="2"/>
+    </row>
+    <row r="203" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>2054</v>
       </c>
@@ -44386,17 +45064,18 @@
       <c r="H203" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I203" s="2" t="s">
+      <c r="I203" s="2"/>
+      <c r="J203" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J203" s="2" t="s">
+      <c r="K203" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="K203" s="2" t="s">
+      <c r="L203" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>2055</v>
       </c>
@@ -44413,15 +45092,16 @@
       </c>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
-      <c r="I204" s="2" t="s">
+      <c r="I204" s="2"/>
+      <c r="J204" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J204" s="2" t="s">
+      <c r="K204" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K204" s="2"/>
-    </row>
-    <row r="205" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L204" s="2"/>
+    </row>
+    <row r="205" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>2056</v>
       </c>
@@ -44440,15 +45120,16 @@
       <c r="H205" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I205" s="2" t="s">
+      <c r="I205" s="2"/>
+      <c r="J205" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J205" s="2" t="s">
+      <c r="K205" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K205" s="2"/>
-    </row>
-    <row r="206" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L205" s="2"/>
+    </row>
+    <row r="206" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>2057</v>
       </c>
@@ -44465,15 +45146,16 @@
       </c>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
-      <c r="I206" s="2" t="s">
+      <c r="I206" s="2"/>
+      <c r="J206" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J206" s="2" t="s">
+      <c r="K206" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K206" s="2"/>
-    </row>
-    <row r="207" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L206" s="2"/>
+    </row>
+    <row r="207" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>2058</v>
       </c>
@@ -44490,15 +45172,16 @@
       </c>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
-      <c r="I207" s="2" t="s">
+      <c r="I207" s="2"/>
+      <c r="J207" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J207" s="2" t="s">
+      <c r="K207" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K207" s="2"/>
-    </row>
-    <row r="208" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L207" s="2"/>
+    </row>
+    <row r="208" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>2059</v>
       </c>
@@ -44519,17 +45202,18 @@
       <c r="H208" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I208" s="2" t="s">
+      <c r="I208" s="2"/>
+      <c r="J208" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J208" s="2" t="s">
+      <c r="K208" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="K208" s="2" t="s">
+      <c r="L208" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>2060</v>
       </c>
@@ -44546,15 +45230,16 @@
       </c>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
-      <c r="I209" s="2" t="s">
+      <c r="I209" s="2"/>
+      <c r="J209" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J209" s="2" t="s">
+      <c r="K209" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K209" s="2"/>
-    </row>
-    <row r="210" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L209" s="2"/>
+    </row>
+    <row r="210" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>2061</v>
       </c>
@@ -44571,15 +45256,16 @@
       </c>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
-      <c r="I210" s="2" t="s">
+      <c r="I210" s="2"/>
+      <c r="J210" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J210" s="2" t="s">
+      <c r="K210" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K210" s="2"/>
-    </row>
-    <row r="211" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L210" s="2"/>
+    </row>
+    <row r="211" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>2062</v>
       </c>
@@ -44600,15 +45286,16 @@
       <c r="H211" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I211" s="2" t="s">
+      <c r="I211" s="2"/>
+      <c r="J211" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J211" s="2" t="s">
+      <c r="K211" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K211" s="2"/>
-    </row>
-    <row r="212" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L211" s="2"/>
+    </row>
+    <row r="212" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>2063</v>
       </c>
@@ -44627,15 +45314,16 @@
       <c r="H212" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I212" s="2" t="s">
+      <c r="I212" s="2"/>
+      <c r="J212" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J212" s="2" t="s">
+      <c r="K212" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K212" s="2"/>
-    </row>
-    <row r="213" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L212" s="2"/>
+    </row>
+    <row r="213" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>2064</v>
       </c>
@@ -44656,15 +45344,16 @@
       </c>
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
-      <c r="I213" s="2" t="s">
+      <c r="I213" s="2"/>
+      <c r="J213" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J213" s="2" t="s">
+      <c r="K213" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K213" s="2"/>
-    </row>
-    <row r="214" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L213" s="2"/>
+    </row>
+    <row r="214" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>2065</v>
       </c>
@@ -44681,15 +45370,16 @@
       </c>
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
-      <c r="I214" s="2" t="s">
+      <c r="I214" s="2"/>
+      <c r="J214" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J214" s="2" t="s">
+      <c r="K214" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K214" s="2"/>
-    </row>
-    <row r="215" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L214" s="2"/>
+    </row>
+    <row r="215" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>2066</v>
       </c>
@@ -44708,15 +45398,16 @@
         <v>1</v>
       </c>
       <c r="H215" s="2"/>
-      <c r="I215" s="2" t="s">
+      <c r="I215" s="2"/>
+      <c r="J215" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J215" s="2" t="s">
+      <c r="K215" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K215" s="2"/>
-    </row>
-    <row r="216" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L215" s="2"/>
+    </row>
+    <row r="216" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>2067</v>
       </c>
@@ -44733,17 +45424,18 @@
       </c>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
-      <c r="I216" s="2" t="s">
+      <c r="I216" s="2"/>
+      <c r="J216" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J216" s="2" t="s">
+      <c r="K216" s="2" t="s">
         <v>2068</v>
       </c>
-      <c r="K216" s="2" t="s">
+      <c r="L216" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>2069</v>
       </c>
@@ -44760,15 +45452,16 @@
       </c>
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
-      <c r="I217" s="2" t="s">
+      <c r="I217" s="2"/>
+      <c r="J217" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J217" s="2" t="s">
+      <c r="K217" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K217" s="2"/>
-    </row>
-    <row r="218" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L217" s="2"/>
+    </row>
+    <row r="218" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>1509</v>
       </c>
@@ -44787,15 +45480,16 @@
         <v>1</v>
       </c>
       <c r="H218" s="2"/>
-      <c r="I218" s="2" t="s">
+      <c r="I218" s="2"/>
+      <c r="J218" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J218" s="2" t="s">
+      <c r="K218" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K218" s="2"/>
-    </row>
-    <row r="219" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L218" s="2"/>
+    </row>
+    <row r="219" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>2070</v>
       </c>
@@ -44812,15 +45506,16 @@
       </c>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
-      <c r="I219" s="2" t="s">
+      <c r="I219" s="2"/>
+      <c r="J219" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J219" s="2" t="s">
+      <c r="K219" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K219" s="2"/>
-    </row>
-    <row r="220" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L219" s="2"/>
+    </row>
+    <row r="220" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>1293</v>
       </c>
@@ -44837,15 +45532,16 @@
       </c>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
-      <c r="I220" s="2" t="s">
+      <c r="I220" s="2"/>
+      <c r="J220" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J220" s="2" t="s">
+      <c r="K220" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K220" s="2"/>
-    </row>
-    <row r="221" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L220" s="2"/>
+    </row>
+    <row r="221" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>1376</v>
       </c>
@@ -44864,15 +45560,16 @@
         <v>1</v>
       </c>
       <c r="H221" s="2"/>
-      <c r="I221" s="2" t="s">
+      <c r="I221" s="2"/>
+      <c r="J221" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J221" s="2" t="s">
+      <c r="K221" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K221" s="2"/>
-    </row>
-    <row r="222" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L221" s="2"/>
+    </row>
+    <row r="222" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>2071</v>
       </c>
@@ -44889,15 +45586,16 @@
       </c>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
-      <c r="I222" s="2" t="s">
+      <c r="I222" s="2"/>
+      <c r="J222" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J222" s="2" t="s">
+      <c r="K222" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K222" s="2"/>
-    </row>
-    <row r="223" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L222" s="2"/>
+    </row>
+    <row r="223" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>1367</v>
       </c>
@@ -44914,15 +45612,16 @@
       </c>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
-      <c r="I223" s="2" t="s">
+      <c r="I223" s="2"/>
+      <c r="J223" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J223" s="2" t="s">
+      <c r="K223" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K223" s="2"/>
-    </row>
-    <row r="224" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L223" s="2"/>
+    </row>
+    <row r="224" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>2072</v>
       </c>
@@ -44939,15 +45638,16 @@
       </c>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
-      <c r="I224" s="2" t="s">
+      <c r="I224" s="2"/>
+      <c r="J224" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J224" s="2" t="s">
+      <c r="K224" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K224" s="2"/>
-    </row>
-    <row r="225" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L224" s="2"/>
+    </row>
+    <row r="225" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>1737</v>
       </c>
@@ -44964,15 +45664,16 @@
       </c>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
-      <c r="I225" s="2" t="s">
+      <c r="I225" s="2"/>
+      <c r="J225" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J225" s="2" t="s">
+      <c r="K225" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K225" s="2"/>
-    </row>
-    <row r="226" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L225" s="2"/>
+    </row>
+    <row r="226" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>1750</v>
       </c>
@@ -44989,15 +45690,16 @@
       </c>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
-      <c r="I226" s="2" t="s">
+      <c r="I226" s="2"/>
+      <c r="J226" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J226" s="2" t="s">
+      <c r="K226" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K226" s="2"/>
-    </row>
-    <row r="227" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L226" s="2"/>
+    </row>
+    <row r="227" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>1527</v>
       </c>
@@ -45014,15 +45716,16 @@
       </c>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
-      <c r="I227" s="2" t="s">
+      <c r="I227" s="2"/>
+      <c r="J227" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J227" s="2" t="s">
+      <c r="K227" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K227" s="2"/>
-    </row>
-    <row r="228" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L227" s="2"/>
+    </row>
+    <row r="228" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>1687</v>
       </c>
@@ -45039,15 +45742,16 @@
       </c>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
-      <c r="I228" s="2" t="s">
+      <c r="I228" s="2"/>
+      <c r="J228" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J228" s="2" t="s">
+      <c r="K228" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K228" s="2"/>
-    </row>
-    <row r="229" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L228" s="2"/>
+    </row>
+    <row r="229" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>2073</v>
       </c>
@@ -45064,15 +45768,16 @@
       </c>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
-      <c r="I229" s="2" t="s">
+      <c r="I229" s="2"/>
+      <c r="J229" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J229" s="2" t="s">
+      <c r="K229" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K229" s="2"/>
-    </row>
-    <row r="230" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L229" s="2"/>
+    </row>
+    <row r="230" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>2074</v>
       </c>
@@ -45089,15 +45794,16 @@
       </c>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
-      <c r="I230" s="2" t="s">
+      <c r="I230" s="2"/>
+      <c r="J230" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J230" s="2" t="s">
+      <c r="K230" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="K230" s="2"/>
-    </row>
-    <row r="231" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L230" s="2"/>
+    </row>
+    <row r="231" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>1440</v>
       </c>
@@ -45114,15 +45820,16 @@
       </c>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
-      <c r="I231" s="2" t="s">
+      <c r="I231" s="2"/>
+      <c r="J231" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J231" s="2" t="s">
+      <c r="K231" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K231" s="2"/>
-    </row>
-    <row r="232" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L231" s="2"/>
+    </row>
+    <row r="232" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>764</v>
       </c>
@@ -45139,15 +45846,16 @@
       </c>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
-      <c r="I232" s="2" t="s">
+      <c r="I232" s="2"/>
+      <c r="J232" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J232" s="2" t="s">
+      <c r="K232" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K232" s="2"/>
-    </row>
-    <row r="233" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L232" s="2"/>
+    </row>
+    <row r="233" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>1748</v>
       </c>
@@ -45164,15 +45872,16 @@
       </c>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
-      <c r="I233" s="2" t="s">
+      <c r="I233" s="2"/>
+      <c r="J233" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J233" s="2" t="s">
+      <c r="K233" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K233" s="2"/>
-    </row>
-    <row r="234" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L233" s="2"/>
+    </row>
+    <row r="234" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>2076</v>
       </c>
@@ -45189,15 +45898,16 @@
       </c>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
-      <c r="I234" s="2" t="s">
+      <c r="I234" s="2"/>
+      <c r="J234" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J234" s="2" t="s">
+      <c r="K234" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K234" s="2"/>
-    </row>
-    <row r="235" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L234" s="2"/>
+    </row>
+    <row r="235" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>2077</v>
       </c>
@@ -45214,15 +45924,16 @@
       </c>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
-      <c r="I235" s="2" t="s">
+      <c r="I235" s="2"/>
+      <c r="J235" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J235" s="2" t="s">
+      <c r="K235" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K235" s="2"/>
-    </row>
-    <row r="236" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L235" s="2"/>
+    </row>
+    <row r="236" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>2078</v>
       </c>
@@ -45239,15 +45950,16 @@
       </c>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
-      <c r="I236" s="2" t="s">
+      <c r="I236" s="2"/>
+      <c r="J236" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J236" s="2" t="s">
+      <c r="K236" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K236" s="2"/>
-    </row>
-    <row r="237" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L236" s="2"/>
+    </row>
+    <row r="237" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>2079</v>
       </c>
@@ -45264,15 +45976,16 @@
       </c>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
-      <c r="I237" s="2" t="s">
+      <c r="I237" s="2"/>
+      <c r="J237" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J237" s="2" t="s">
+      <c r="K237" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K237" s="2"/>
-    </row>
-    <row r="238" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L237" s="2"/>
+    </row>
+    <row r="238" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>1553</v>
       </c>
@@ -45289,15 +46002,16 @@
       </c>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
-      <c r="I238" s="2" t="s">
+      <c r="I238" s="2"/>
+      <c r="J238" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J238" s="2" t="s">
+      <c r="K238" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K238" s="2"/>
-    </row>
-    <row r="239" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L238" s="2"/>
+    </row>
+    <row r="239" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>2080</v>
       </c>
@@ -45314,15 +46028,16 @@
       </c>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
-      <c r="I239" s="2" t="s">
+      <c r="I239" s="2"/>
+      <c r="J239" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J239" s="2" t="s">
+      <c r="K239" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K239" s="2"/>
-    </row>
-    <row r="240" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L239" s="2"/>
+    </row>
+    <row r="240" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>1630</v>
       </c>
@@ -45339,15 +46054,16 @@
       </c>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
-      <c r="I240" s="2" t="s">
+      <c r="I240" s="2"/>
+      <c r="J240" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J240" s="2" t="s">
+      <c r="K240" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K240" s="2"/>
-    </row>
-    <row r="241" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L240" s="2"/>
+    </row>
+    <row r="241" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>1592</v>
       </c>
@@ -45364,15 +46080,16 @@
       </c>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
-      <c r="I241" s="2" t="s">
+      <c r="I241" s="2"/>
+      <c r="J241" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J241" s="2" t="s">
+      <c r="K241" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K241" s="2"/>
-    </row>
-    <row r="242" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L241" s="2"/>
+    </row>
+    <row r="242" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>2081</v>
       </c>
@@ -45389,15 +46106,16 @@
       </c>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
-      <c r="I242" s="2" t="s">
+      <c r="I242" s="2"/>
+      <c r="J242" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J242" s="2" t="s">
+      <c r="K242" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K242" s="2"/>
-    </row>
-    <row r="243" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L242" s="2"/>
+    </row>
+    <row r="243" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>2082</v>
       </c>
@@ -45414,15 +46132,16 @@
       </c>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
-      <c r="I243" s="2" t="s">
+      <c r="I243" s="2"/>
+      <c r="J243" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J243" s="2" t="s">
+      <c r="K243" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K243" s="2"/>
-    </row>
-    <row r="244" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L243" s="2"/>
+    </row>
+    <row r="244" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>2083</v>
       </c>
@@ -45439,15 +46158,16 @@
       </c>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
-      <c r="I244" s="2" t="s">
+      <c r="I244" s="2"/>
+      <c r="J244" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J244" s="2" t="s">
+      <c r="K244" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K244" s="2"/>
-    </row>
-    <row r="245" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L244" s="2"/>
+    </row>
+    <row r="245" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>2084</v>
       </c>
@@ -45466,15 +46186,16 @@
         <v>1</v>
       </c>
       <c r="H245" s="2"/>
-      <c r="I245" s="2" t="s">
+      <c r="I245" s="2"/>
+      <c r="J245" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J245" s="2" t="s">
+      <c r="K245" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K245" s="2"/>
-    </row>
-    <row r="246" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L245" s="2"/>
+    </row>
+    <row r="246" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>2085</v>
       </c>
@@ -45491,15 +46212,16 @@
       </c>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
-      <c r="I246" s="2" t="s">
+      <c r="I246" s="2"/>
+      <c r="J246" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J246" s="2" t="s">
+      <c r="K246" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K246" s="2"/>
-    </row>
-    <row r="247" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L246" s="2"/>
+    </row>
+    <row r="247" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>2086</v>
       </c>
@@ -45516,15 +46238,16 @@
       </c>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
-      <c r="I247" s="2" t="s">
+      <c r="I247" s="2"/>
+      <c r="J247" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J247" s="2" t="s">
+      <c r="K247" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K247" s="2"/>
-    </row>
-    <row r="248" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L247" s="2"/>
+    </row>
+    <row r="248" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>2087</v>
       </c>
@@ -45541,15 +46264,16 @@
       </c>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
-      <c r="I248" s="2" t="s">
+      <c r="I248" s="2"/>
+      <c r="J248" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J248" s="2" t="s">
+      <c r="K248" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K248" s="2"/>
-    </row>
-    <row r="249" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L248" s="2"/>
+    </row>
+    <row r="249" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>2088</v>
       </c>
@@ -45566,15 +46290,16 @@
       </c>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
-      <c r="I249" s="2" t="s">
+      <c r="I249" s="2"/>
+      <c r="J249" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J249" s="2" t="s">
+      <c r="K249" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K249" s="2"/>
-    </row>
-    <row r="250" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L249" s="2"/>
+    </row>
+    <row r="250" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>1603</v>
       </c>
@@ -45591,15 +46316,16 @@
       </c>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
-      <c r="I250" s="2" t="s">
+      <c r="I250" s="2"/>
+      <c r="J250" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J250" s="2" t="s">
+      <c r="K250" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K250" s="2"/>
-    </row>
-    <row r="251" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L250" s="2"/>
+    </row>
+    <row r="251" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>2089</v>
       </c>
@@ -45616,15 +46342,16 @@
       </c>
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
-      <c r="I251" s="2" t="s">
+      <c r="I251" s="2"/>
+      <c r="J251" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J251" s="2" t="s">
+      <c r="K251" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K251" s="2"/>
-    </row>
-    <row r="252" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L251" s="2"/>
+    </row>
+    <row r="252" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>2090</v>
       </c>
@@ -45641,15 +46368,16 @@
       </c>
       <c r="G252" s="2"/>
       <c r="H252" s="2"/>
-      <c r="I252" s="2" t="s">
+      <c r="I252" s="2"/>
+      <c r="J252" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J252" s="2" t="s">
+      <c r="K252" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K252" s="2"/>
-    </row>
-    <row r="253" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L252" s="2"/>
+    </row>
+    <row r="253" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>2091</v>
       </c>
@@ -45666,15 +46394,16 @@
       </c>
       <c r="G253" s="2"/>
       <c r="H253" s="2"/>
-      <c r="I253" s="2" t="s">
+      <c r="I253" s="2"/>
+      <c r="J253" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J253" s="2" t="s">
+      <c r="K253" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K253" s="2"/>
-    </row>
-    <row r="254" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L253" s="2"/>
+    </row>
+    <row r="254" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>2092</v>
       </c>
@@ -45691,15 +46420,16 @@
       </c>
       <c r="G254" s="2"/>
       <c r="H254" s="2"/>
-      <c r="I254" s="2" t="s">
+      <c r="I254" s="2"/>
+      <c r="J254" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J254" s="2" t="s">
+      <c r="K254" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K254" s="2"/>
-    </row>
-    <row r="255" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L254" s="2"/>
+    </row>
+    <row r="255" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>2093</v>
       </c>
@@ -45716,15 +46446,16 @@
       </c>
       <c r="G255" s="2"/>
       <c r="H255" s="2"/>
-      <c r="I255" s="2" t="s">
+      <c r="I255" s="2"/>
+      <c r="J255" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J255" s="2" t="s">
+      <c r="K255" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K255" s="2"/>
-    </row>
-    <row r="256" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L255" s="2"/>
+    </row>
+    <row r="256" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>2094</v>
       </c>
@@ -45741,15 +46472,16 @@
       </c>
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
-      <c r="I256" s="2" t="s">
+      <c r="I256" s="2"/>
+      <c r="J256" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J256" s="2" t="s">
+      <c r="K256" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="K256" s="2"/>
-    </row>
-    <row r="257" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L256" s="2"/>
+    </row>
+    <row r="257" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>1305</v>
       </c>
@@ -45766,15 +46498,16 @@
       </c>
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
-      <c r="I257" s="2" t="s">
+      <c r="I257" s="2"/>
+      <c r="J257" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J257" s="2" t="s">
+      <c r="K257" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K257" s="2"/>
-    </row>
-    <row r="258" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L257" s="2"/>
+    </row>
+    <row r="258" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>2095</v>
       </c>
@@ -45791,15 +46524,16 @@
       </c>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
-      <c r="I258" s="2" t="s">
+      <c r="I258" s="2"/>
+      <c r="J258" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J258" s="2" t="s">
+      <c r="K258" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K258" s="2"/>
-    </row>
-    <row r="259" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L258" s="2"/>
+    </row>
+    <row r="259" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>2096</v>
       </c>
@@ -45816,15 +46550,16 @@
       </c>
       <c r="G259" s="2"/>
       <c r="H259" s="2"/>
-      <c r="I259" s="2" t="s">
+      <c r="I259" s="2"/>
+      <c r="J259" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J259" s="2" t="s">
+      <c r="K259" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K259" s="2"/>
-    </row>
-    <row r="260" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L259" s="2"/>
+    </row>
+    <row r="260" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>2097</v>
       </c>
@@ -45841,15 +46576,16 @@
       </c>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
-      <c r="I260" s="2" t="s">
+      <c r="I260" s="2"/>
+      <c r="J260" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J260" s="2" t="s">
+      <c r="K260" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K260" s="2"/>
-    </row>
-    <row r="261" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L260" s="2"/>
+    </row>
+    <row r="261" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>2098</v>
       </c>
@@ -45866,15 +46602,16 @@
       </c>
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
-      <c r="I261" s="2" t="s">
+      <c r="I261" s="2"/>
+      <c r="J261" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J261" s="2" t="s">
+      <c r="K261" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K261" s="2"/>
-    </row>
-    <row r="262" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L261" s="2"/>
+    </row>
+    <row r="262" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>2099</v>
       </c>
@@ -45891,17 +46628,18 @@
       </c>
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
-      <c r="I262" s="2" t="s">
+      <c r="I262" s="2"/>
+      <c r="J262" s="2" t="s">
         <v>2038</v>
       </c>
-      <c r="J262" s="2" t="s">
+      <c r="K262" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="K262" s="2" t="s">
+      <c r="L262" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>1635</v>
       </c>
@@ -45918,15 +46656,16 @@
       </c>
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
-      <c r="I263" s="2" t="s">
+      <c r="I263" s="2"/>
+      <c r="J263" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J263" s="2" t="s">
+      <c r="K263" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K263" s="2"/>
-    </row>
-    <row r="264" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L263" s="2"/>
+    </row>
+    <row r="264" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>1882</v>
       </c>
@@ -45945,15 +46684,16 @@
         <v>1</v>
       </c>
       <c r="H264" s="2"/>
-      <c r="I264" s="2" t="s">
+      <c r="I264" s="2"/>
+      <c r="J264" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J264" s="2" t="s">
+      <c r="K264" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K264" s="2"/>
-    </row>
-    <row r="265" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L264" s="2"/>
+    </row>
+    <row r="265" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>2100</v>
       </c>
@@ -45970,15 +46710,16 @@
       </c>
       <c r="G265" s="2"/>
       <c r="H265" s="2"/>
-      <c r="I265" s="2" t="s">
+      <c r="I265" s="2"/>
+      <c r="J265" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J265" s="2" t="s">
+      <c r="K265" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K265" s="2"/>
-    </row>
-    <row r="266" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L265" s="2"/>
+    </row>
+    <row r="266" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>2101</v>
       </c>
@@ -45995,15 +46736,16 @@
       </c>
       <c r="G266" s="2"/>
       <c r="H266" s="2"/>
-      <c r="I266" s="2" t="s">
+      <c r="I266" s="2"/>
+      <c r="J266" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J266" s="2" t="s">
+      <c r="K266" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K266" s="2"/>
-    </row>
-    <row r="267" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L266" s="2"/>
+    </row>
+    <row r="267" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>2102</v>
       </c>
@@ -46020,15 +46762,16 @@
       </c>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
-      <c r="I267" s="2" t="s">
+      <c r="I267" s="2"/>
+      <c r="J267" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J267" s="2" t="s">
+      <c r="K267" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K267" s="2"/>
-    </row>
-    <row r="268" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L267" s="2"/>
+    </row>
+    <row r="268" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>2103</v>
       </c>
@@ -46045,15 +46788,16 @@
       </c>
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
-      <c r="I268" s="2" t="s">
+      <c r="I268" s="2"/>
+      <c r="J268" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J268" s="2" t="s">
+      <c r="K268" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K268" s="2"/>
-    </row>
-    <row r="269" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L268" s="2"/>
+    </row>
+    <row r="269" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>2104</v>
       </c>
@@ -46070,17 +46814,18 @@
       </c>
       <c r="G269" s="2"/>
       <c r="H269" s="2"/>
-      <c r="I269" s="2" t="s">
+      <c r="I269" s="2"/>
+      <c r="J269" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J269" s="2" t="s">
+      <c r="K269" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="K269" s="2" t="s">
+      <c r="L269" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>2105</v>
       </c>
@@ -46099,15 +46844,16 @@
         <v>1</v>
       </c>
       <c r="H270" s="2"/>
-      <c r="I270" s="2" t="s">
+      <c r="I270" s="2"/>
+      <c r="J270" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J270" s="2" t="s">
+      <c r="K270" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K270" s="2"/>
-    </row>
-    <row r="271" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L270" s="2"/>
+    </row>
+    <row r="271" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>2106</v>
       </c>
@@ -46126,15 +46872,16 @@
         <v>1</v>
       </c>
       <c r="H271" s="2"/>
-      <c r="I271" s="2" t="s">
+      <c r="I271" s="2"/>
+      <c r="J271" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J271" s="2" t="s">
+      <c r="K271" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="K271" s="2"/>
-    </row>
-    <row r="272" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L271" s="2"/>
+    </row>
+    <row r="272" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>2107</v>
       </c>
@@ -46151,15 +46898,16 @@
       </c>
       <c r="G272" s="2"/>
       <c r="H272" s="2"/>
-      <c r="I272" s="2" t="s">
+      <c r="I272" s="2"/>
+      <c r="J272" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J272" s="2" t="s">
+      <c r="K272" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K272" s="2"/>
-    </row>
-    <row r="273" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L272" s="2"/>
+    </row>
+    <row r="273" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>1667</v>
       </c>
@@ -46176,15 +46924,16 @@
       </c>
       <c r="G273" s="2"/>
       <c r="H273" s="2"/>
-      <c r="I273" s="2" t="s">
+      <c r="I273" s="2"/>
+      <c r="J273" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J273" s="2" t="s">
+      <c r="K273" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K273" s="2"/>
-    </row>
-    <row r="274" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L273" s="2"/>
+    </row>
+    <row r="274" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>2108</v>
       </c>
@@ -46201,15 +46950,16 @@
       </c>
       <c r="G274" s="2"/>
       <c r="H274" s="2"/>
-      <c r="I274" s="2" t="s">
+      <c r="I274" s="2"/>
+      <c r="J274" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J274" s="2" t="s">
+      <c r="K274" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K274" s="2"/>
-    </row>
-    <row r="275" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L274" s="2"/>
+    </row>
+    <row r="275" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>2109</v>
       </c>
@@ -46226,15 +46976,16 @@
       </c>
       <c r="G275" s="2"/>
       <c r="H275" s="2"/>
-      <c r="I275" s="2" t="s">
+      <c r="I275" s="2"/>
+      <c r="J275" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J275" s="2" t="s">
+      <c r="K275" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K275" s="2"/>
-    </row>
-    <row r="276" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L275" s="2"/>
+    </row>
+    <row r="276" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>2110</v>
       </c>
@@ -46251,15 +47002,16 @@
       </c>
       <c r="G276" s="2"/>
       <c r="H276" s="2"/>
-      <c r="I276" s="2" t="s">
+      <c r="I276" s="2"/>
+      <c r="J276" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J276" s="2" t="s">
+      <c r="K276" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K276" s="2"/>
-    </row>
-    <row r="277" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L276" s="2"/>
+    </row>
+    <row r="277" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>2111</v>
       </c>
@@ -46276,15 +47028,16 @@
       </c>
       <c r="G277" s="2"/>
       <c r="H277" s="2"/>
-      <c r="I277" s="2" t="s">
+      <c r="I277" s="2"/>
+      <c r="J277" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J277" s="2" t="s">
+      <c r="K277" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K277" s="2"/>
-    </row>
-    <row r="278" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L277" s="2"/>
+    </row>
+    <row r="278" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>2112</v>
       </c>
@@ -46301,15 +47054,16 @@
       </c>
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
-      <c r="I278" s="2" t="s">
+      <c r="I278" s="2"/>
+      <c r="J278" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="J278" s="2" t="s">
+      <c r="K278" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K278" s="2"/>
-    </row>
-    <row r="279" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L278" s="2"/>
+    </row>
+    <row r="279" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>2113</v>
       </c>
@@ -46326,15 +47080,16 @@
       </c>
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
-      <c r="I279" s="2" t="s">
+      <c r="I279" s="2"/>
+      <c r="J279" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J279" s="2" t="s">
+      <c r="K279" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K279" s="2"/>
-    </row>
-    <row r="280" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L279" s="2"/>
+    </row>
+    <row r="280" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>2114</v>
       </c>
@@ -46351,15 +47106,16 @@
       </c>
       <c r="G280" s="2"/>
       <c r="H280" s="2"/>
-      <c r="I280" s="2" t="s">
+      <c r="I280" s="2"/>
+      <c r="J280" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J280" s="2" t="s">
+      <c r="K280" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="K280" s="2"/>
-    </row>
-    <row r="281" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L280" s="2"/>
+    </row>
+    <row r="281" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>2115</v>
       </c>
@@ -46376,13 +47132,14 @@
       </c>
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
-      <c r="I281" s="2" t="s">
+      <c r="I281" s="2"/>
+      <c r="J281" s="2" t="s">
         <v>1918</v>
       </c>
-      <c r="J281" s="2" t="s">
+      <c r="K281" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K281" s="2"/>
+      <c r="L281" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/assets/data/generatordata.xlsx
+++ b/assets/data/generatordata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mthak\Desktop\pf2e-generator\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACE15F5-FCB4-4AA2-84CC-29EEB3B1E559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62554153-024D-4358-878F-084062FEB87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{12225E00-D84F-438D-9971-6445E1072934}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12225E00-D84F-438D-9971-6445E1072934}"/>
   </bookViews>
   <sheets>
     <sheet name="Ancestries" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9156" uniqueCount="2158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9210" uniqueCount="2166">
   <si>
     <t>ancestry</t>
   </si>
@@ -6522,6 +6522,30 @@
   </si>
   <si>
     <t>specific_weapon</t>
+  </si>
+  <si>
+    <t>rarity_garund</t>
+  </si>
+  <si>
+    <t>rarity_tianxia</t>
+  </si>
+  <si>
+    <t>rarity_avistan</t>
+  </si>
+  <si>
+    <t>Iblydos</t>
+  </si>
+  <si>
+    <t>Kelesh</t>
+  </si>
+  <si>
+    <t>Vudra</t>
+  </si>
+  <si>
+    <t>rarity_casmaron</t>
+  </si>
+  <si>
+    <t>rarity_arcadia</t>
   </si>
 </sst>
 </file>
@@ -6558,7 +6582,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -6581,11 +6605,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6604,6 +6639,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6939,15 +6977,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C3D1795-EDE3-4633-8891-F0CE552D71CB}">
-  <dimension ref="A1:D51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I51"/>
+  <sheetFormatPr defaultColWidth="102.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -6955,13 +6997,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2160</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2158</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2159</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2165</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2164</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>34</v>
       </c>
@@ -6969,11 +7026,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>46</v>
       </c>
@@ -6981,11 +7043,16 @@
         <v>7</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>54</v>
       </c>
@@ -6994,10 +7061,17 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>62</v>
       </c>
@@ -7006,10 +7080,17 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>71</v>
       </c>
@@ -7017,11 +7098,16 @@
         <v>7</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>79</v>
       </c>
@@ -7029,11 +7115,16 @@
         <v>7</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>83</v>
       </c>
@@ -7041,11 +7132,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>97</v>
       </c>
@@ -7053,23 +7149,39 @@
         <v>7</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>111</v>
       </c>
@@ -7077,11 +7189,20 @@
         <v>11</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>122</v>
       </c>
@@ -7090,10 +7211,23 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>130</v>
       </c>
@@ -7102,10 +7236,21 @@
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>137</v>
       </c>
@@ -7114,10 +7259,21 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>141</v>
       </c>
@@ -7126,10 +7282,19 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>149</v>
       </c>
@@ -7138,10 +7303,21 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>156</v>
       </c>
@@ -7149,11 +7325,18 @@
         <v>11</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>163</v>
       </c>
@@ -7162,10 +7345,17 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>174</v>
       </c>
@@ -7174,10 +7364,17 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>184</v>
       </c>
@@ -7185,11 +7382,16 @@
         <v>11</v>
       </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>190</v>
       </c>
@@ -7197,23 +7399,39 @@
         <v>11</v>
       </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>197</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="D22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>205</v>
       </c>
@@ -7221,35 +7439,64 @@
         <v>11</v>
       </c>
       <c r="C23" s="2"/>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="2"/>
+      <c r="E23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="2"/>
+      <c r="C24" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="D24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="2"/>
+      <c r="C25" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="D25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>222</v>
       </c>
@@ -7257,11 +7504,18 @@
         <v>11</v>
       </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="2"/>
+      <c r="E26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>229</v>
       </c>
@@ -7270,34 +7524,61 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>236</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2" t="s">
+      <c r="C28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>241</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="2"/>
+      <c r="C29" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="D29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>247</v>
       </c>
@@ -7305,11 +7586,16 @@
         <v>31</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>254</v>
       </c>
@@ -7317,11 +7603,16 @@
         <v>31</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>260</v>
       </c>
@@ -7329,11 +7620,16 @@
         <v>31</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>265</v>
       </c>
@@ -7341,11 +7637,16 @@
         <v>31</v>
       </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>270</v>
       </c>
@@ -7353,11 +7654,16 @@
         <v>31</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>276</v>
       </c>
@@ -7365,11 +7671,16 @@
         <v>31</v>
       </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>283</v>
       </c>
@@ -7377,11 +7688,16 @@
         <v>31</v>
       </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>291</v>
       </c>
@@ -7389,11 +7705,16 @@
         <v>31</v>
       </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>296</v>
       </c>
@@ -7401,11 +7722,16 @@
         <v>31</v>
       </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>302</v>
       </c>
@@ -7413,11 +7739,16 @@
         <v>31</v>
       </c>
       <c r="C39" s="2"/>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>308</v>
       </c>
@@ -7425,11 +7756,18 @@
         <v>31</v>
       </c>
       <c r="C40" s="2"/>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>314</v>
       </c>
@@ -7437,11 +7775,16 @@
         <v>31</v>
       </c>
       <c r="C41" s="2"/>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>322</v>
       </c>
@@ -7449,11 +7792,16 @@
         <v>31</v>
       </c>
       <c r="C42" s="2"/>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>328</v>
       </c>
@@ -7462,24 +7810,36 @@
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>334</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="I44" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>340</v>
       </c>
@@ -7487,11 +7847,16 @@
         <v>31</v>
       </c>
       <c r="C45" s="2"/>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>348</v>
       </c>
@@ -7499,11 +7864,16 @@
         <v>31</v>
       </c>
       <c r="C46" s="2"/>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>359</v>
       </c>
@@ -7511,11 +7881,16 @@
         <v>31</v>
       </c>
       <c r="C47" s="2"/>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>365</v>
       </c>
@@ -7523,11 +7898,16 @@
         <v>31</v>
       </c>
       <c r="C48" s="2"/>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>370</v>
       </c>
@@ -7535,11 +7915,18 @@
         <v>31</v>
       </c>
       <c r="C49" s="2"/>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>377</v>
       </c>
@@ -7547,11 +7934,16 @@
         <v>31</v>
       </c>
       <c r="C50" s="2"/>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>384</v>
       </c>
@@ -7559,7 +7951,12 @@
         <v>31</v>
       </c>
       <c r="C51" s="2"/>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -31044,7 +31441,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF39BE0-A267-465D-94EE-F339AD54ABEF}">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr defaultColWidth="64.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
@@ -31776,12 +32173,28 @@
     </row>
     <row r="81" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>1288</v>
+        <v>2161</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>1288</v>
       </c>
       <c r="C81" s="2"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="7" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="7" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>1288</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
